--- a/docs/Corridor_Communicator_API_Inventory.xlsx
+++ b/docs/Corridor_Communicator_API_Inventory.xlsx
@@ -12,12 +12,18 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Feed Registry" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External APIs Consumed" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Published Feeds" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Camera Sources" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DMS + Device Sources" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation Logic" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Internal REST API'!$A$1:$I$512</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'State Feed Registry'!$A$1:$G$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'External APIs Consumed'!$A$1:$G$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Published Feeds'!$A$1:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Camera Sources'!$A$1:$H$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'DMS + Device Sources'!$A$1:$J$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Validation Logic'!$A$1:$G$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,7 +32,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,6 +77,18 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="005B6B8C"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="008A3A00"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="006B1F8C"/>
     </font>
   </fonts>
   <fills count="4">
@@ -117,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -159,6 +177,30 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -526,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C118"/>
+  <dimension ref="A1:C123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2105,6 +2147,34 @@
       <c r="A118" t="inlineStr">
         <is>
           <t>Published Feeds - what the platform emits for others to consume</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Camera / DMS / validation tabs</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Camera Sources - 15 state camera networks with live unit counts (pulled 2026-09-03)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>DMS + Device Sources - 18 state DMS / arrow-board feeds; 8 are key-gated and currently skipped</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Validation Logic - every validation rule and threshold, ingest through CWZ 1.0 composition</t>
         </is>
       </c>
     </row>
@@ -26470,7 +26540,7 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>511 sites for ID, GA, NY, AZ, CA, FL, MN, NC, NV, UT, PA, LA, New England, Austin TX</t>
+          <t>Itemized on the 'Camera Sources' tab - 15 state networks, 21941 cameras</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
@@ -26507,7 +26577,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>511/AGOL device endpoints for ID, LA, NJ, NY, WI, ME, AZ, MD, CA, FL, PA, OK, NM, NC, NV, UT, WA</t>
+          <t>Itemized on the 'DMS + Device Sources' tab - 18 state feeds, 4601 signs/devices from the 10 keyless ones</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -27438,4 +27508,3633 @@
   <autoFilter ref="A1:F9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Agency / network</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Adapter family</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Endpoint</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Live pull 2026-09-03</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Cameras returned</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>With still image</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>IBI/511 cameras (POST)</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>https://az511.com/ (List/GetData cameras)</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>644</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>644</v>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>camera-adapters.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Caltrans CWWP2 (12 districts)</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>https://cwwp2.dot.ca.gov/data/d&lt;N&gt;/cctv/cctvStatusD&lt;NN&gt;.json</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>3340</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>3340</v>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>camera-adapters.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>ArcGIS FeatureServer</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>https://gis.fdot.gov/arcgis/rest/services/DIVAS_Cameras/FeatureServer/0/query</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1669</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>1669</v>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>camera-adapters.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>IBI/511 cameras (POST)</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>https://511ga.org/ (List/GetData cameras)</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>4043</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>4043</v>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>camera-adapters.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Idaho</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>IBI/511 cameras (POST)</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>https://511.idaho.gov/ (List/GetData cameras)</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>457</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>457</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>camera-adapters.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>ArcGIS FeatureServer</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>https://services.arcgis.com/8lRhdTsQyJpO52F1/.../Traffic_Cameras_View/FeatureServer/0/query</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>1252</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>1252</v>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>camera-adapters.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Louisiana</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>IBI/511 cameras (POST)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>https://www.511la.org/ (List/GetData cameras)</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>336</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>336</v>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>camera-adapters.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Maine / New England</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>IBI/511 cameras (POST)</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>https://newengland511.org/ (List/GetData cameras)</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>405</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>405</v>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>camera-adapters.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>MN</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Minnesota</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>CARS cameras_v1</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>https://mntg.carsprogram.org/cameras_v1/api/cameras</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1528</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>1528</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>camera-adapters.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Nevada</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>IBI/511 cameras (POST)</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>https://www.nvroads.com/ (List/GetData cameras)</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>640</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>640</v>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>camera-adapters.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>511NY getcameras</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>https://511ny.org/api/getcameras?format=json</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1871</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>1871</v>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>camera-adapters.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>IBI/511 cameras (POST)</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>https://www.drivenc.gov/ (List/GetData cameras)</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>1140</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>1140</v>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>camera-adapters.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>IBI/511 cameras (POST)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>https://www.511pa.com/ (List/GetData cameras)</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>1536</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>1536</v>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>camera-adapters.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Texas (Austin)</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Socrata open data</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>https://data.austintexas.gov/resource/b4k4-adkb.json (images: cctv.austinmobility.io)</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>1005</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>1005</v>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>camera-adapters.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Utah</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>IBI/511 cameras (POST)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>https://www.udottraffic.utah.gov/ (List/GetData cameras)</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>2075</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>2075</v>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>camera-adapters.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr"/>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr"/>
+      <c r="D17" s="17" t="inlineStr"/>
+      <c r="E17" s="17" t="inlineStr"/>
+      <c r="F17" s="17" t="n">
+        <v>21941</v>
+      </c>
+      <c r="G17" s="17" t="n">
+        <v>21941</v>
+      </c>
+      <c r="H17" s="17" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H17"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Agency</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Adapter family</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Endpoint</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Live pull 2026-09-03</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Signs / devices</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Actively displaying</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Portable units</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Key required</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Iowa (DMS corroboration validator)</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>ArcGIS FeatureServer</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>https://services.arcgis.com/8lRhdTsQyJpO52F1/ArcGIS/rest/services/DMS_View/FeatureServer/0/query</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>not counted in this pull</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr"/>
+      <c r="G2" s="8" t="inlineStr"/>
+      <c r="H2" s="8" t="inlineStr"/>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>Primary DMS source for the DMS validator + device ingest; 10-min cache</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>CARS/OneStop 511</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>https://az511.com/api/v2/get/messagesigns</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>SKIPPED - no key</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr"/>
+      <c r="H3" s="5" t="inlineStr"/>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Free key required</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Caltrans CWWP2 CMS (12 districts)</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>https://cwwp2.dot.ca.gov/data/d&lt;N&gt;/cms/cmsStatusD&lt;NN&gt;.json</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>1016</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>Some districts intermittently 500 and are skipped</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>ArcGIS FeatureServer</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>https://gis.fdot.gov/arcgis/rest/services/DIVAS_MessageBoard/FeatureServer/0/query</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>1047</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>520</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Fixed DMS with live message text</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Idaho</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>CARS/OneStop 511</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>https://511.idaho.gov/api/v2/get/messagesigns</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>SKIPPED - no key</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr"/>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>Free key required</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Kentucky</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>ArcGIS FeatureServer</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>https://services2.arcgis.com/CcI36Pduqd0OR4W9/.../dmsSigns_2020/FeatureServer/0/query</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Fixed DMS with live message text</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Louisiana</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>CARS/OneStop 511</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>https://511la.org/api/v2/get/messagesigns</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>SKIPPED - no key</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr"/>
+      <c r="G8" s="8" t="inlineStr"/>
+      <c r="H8" s="8" t="inlineStr"/>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>Free key required</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>ArcGIS MapServer</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>https://arcgisserver.maine.gov/arcgis/rest/services/mdot/MaineDOT_Dynamic/MapServer/111/query</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Portable = trailer installation type</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Maryland</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>ArcGIS MapServer (CHART)</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>https://chartimap1.sha.maryland.gov/arcgis/rest/services/CHART/DMS/MapServer/0/query</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>295</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>212</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>Route/direction parsed from location string</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Nevada</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>CARS/OneStop 511</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>https://www.nvroads.com/api/v2/get/messagesigns</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>SKIPPED - no key</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Free key required</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>CARS/OneStop 511</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>https://511nj.org/api/getmessagesigns</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>SKIPPED - no key</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr"/>
+      <c r="G12" s="8" t="inlineStr"/>
+      <c r="H12" s="8" t="inlineStr"/>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>Free key required</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Custom REST (NMRoads)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>https://servicev4.nmroads.com/RealMapWAR/GetMessageSigns</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>ERROR: certificate has expired</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>TLS certificate expired as of the pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>CARS/OneStop 511 (keyless path)</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>https://511ny.org/api/getmessagesigns?format=json</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>919</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>919</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>Keyless; 175 portable units detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>CARS/OneStop 511</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>https://www.drivenc.gov/api/v2/get/messagesigns</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>SKIPPED - no key</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Free key required</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Oklahoma</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Custom REST (oktraffic.org)</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>https://oktraffic.org/api/Devices + /api/DmsStatuses</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>167</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>51</v>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>NTCIP MULTI tags stripped from message text</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>ArcGIS MapServer</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>https://gis.penndot.gov/arcgis/rest/services/tsams/tsams/MapServer/17/query</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>962</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>109</v>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Portable = trailer / Type A-B structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Utah</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>CARS/OneStop 511</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>https://www.udottraffic.utah.gov/api/v2/get/messagesigns</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>SKIPPED - no key</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr"/>
+      <c r="G18" s="8" t="inlineStr"/>
+      <c r="H18" s="8" t="inlineStr"/>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>Free key required</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>WZDx v4 Device Feed</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>https://wzdx.wsdot.wa.gov/api/v4/DeviceFeed</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Only true WZDx device feed in the set - real arrow boards</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>WI</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>CARS/OneStop 511</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>https://511wi.gov/api/v2/get/messagesigns</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>SKIPPED - no key</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr"/>
+      <c r="G20" s="8" t="inlineStr"/>
+      <c r="H20" s="8" t="inlineStr"/>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>Free key required</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr"/>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>TOTAL (feeds that returned)</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr"/>
+      <c r="D21" s="18" t="inlineStr"/>
+      <c r="E21" s="18" t="inlineStr"/>
+      <c r="F21" s="18" t="n">
+        <v>4601</v>
+      </c>
+      <c r="G21" s="18" t="n">
+        <v>1789</v>
+      </c>
+      <c r="H21" s="18" t="n">
+        <v>429</v>
+      </c>
+      <c r="I21" s="18" t="inlineStr"/>
+      <c r="J21" s="18" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J20"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="74" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>What it validates</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Rule / threshold as coded</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>On fail</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Output field</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Implemented in</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>0. Ingest / normalize</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Route normalization</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Free-text route strings from 37 different feeds resolve to one canonical route id</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Regex ladder: I-nnn first (ramp strings embed it), then US-nnn, then &lt;ST&gt;-nnn. 'I 380', 'I-380', 'RAMP: I 80E TO 100TH ST' all -&gt; 'I-380'/'I-80'</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Returns null -&gt; the record cannot be route-matched and is skipped by the matcher</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>route / rawRoute</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>device-workzone-matcher.js normalizeRoute</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>0. Ingest / normalize</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Direction normalization</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Carriageway direction is one of N/S/E/W/BOTH</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>First letter after uppercasing; 'Both'/'B' -&gt; BOTH; anything else -&gt; null (neutral, not a reject)</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>null = unknown, treated as neutral rather than a mismatch</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>direction</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>device-workzone-matcher.js normalizeDir</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>0. Ingest / normalize</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Coordinate sanity</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Lat/lon are real and not a null-island artifact</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Both finite, not (0,0), |lat| &lt;= 90, |lon| &lt;= 180</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Record dropped at normalize()</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>device-adapters.js normalize</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>1. Geometry</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Missing content</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Event has geometry and some human content</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>No geometry -&gt; drop. Empty description AND empty location -&gt; drop</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Event filtered out entirely</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>geometry-validator.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>1. Geometry</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Fallback-geometry rejection</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Geometry is not an interpolated straight line masquerading as road shape</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>geometrySource in ('straight_line','straight') -&gt; drop</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Event filtered out</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>geometry-validator.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>1. Geometry</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>2-point LineString collapse</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>A 2-point line carries no road shape, so it must not render as a road</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>LineString with exactly 2 coordinates -&gt; converted to a Point at the midpoint</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Downgraded to a marker, not dropped</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>_geometryFixed</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>geometry-validator.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>1. Geometry</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Curvature test (long lines)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>A very long 'closure' line actually follows the road rather than cutting across it</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>chord &gt; 50 mi AND path length / chord &lt; 1.05 (under 5% curvature) -&gt; drop</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Event filtered out</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>geometry-validator.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>1. Geometry</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Type validity</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Point/LineString/Polygon/Multi* are structurally well formed</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Point needs 2 coords; LineString &gt;= 2; Polygon outer ring &gt;= 4; Multi* non-empty; unknown type -&gt; drop</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Event filtered out</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>geometry-validator.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>2. Feed quality (DQI)</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Completeness (20%)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Required WZDx fields are actually populated across the feed</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Share of events carrying end time, description, geometry, severity, lanes affected</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Lowers the feed's DQI and letter grade</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>dqi.completeness</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>feed-quality-scorer.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>2. Feed quality (DQI)</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Freshness (15%)</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>The feed is being updated and events are not stale</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Update latency + stale-event share</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Lowers DQI</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>dqi.freshness</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>feed-quality-scorer.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>2. Feed quality (DQI)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Accuracy (20%)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Geometry validates and the payload matches schema</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Geometry validation pass rate + schema compliance</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Lowers DQI</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>dqi.accuracy</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>feed-quality-scorer.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>2. Feed quality (DQI)</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Availability (15%)</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>The endpoint answers reliably</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Fetch success / failure history per feed key</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Lowers DQI; feeds an outage signal</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>dqi.availability</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>feed-quality-scorer.js + feed-tracking-service.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>2. Feed quality (DQI)</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Standardization (15%)</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>WZDx compliance, valid event types, ITIS codes</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Share of events using spec-valid enumerations</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Lowers DQI</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>dqi.standardization</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>feed-quality-scorer.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>2. Feed quality (DQI)</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Timeliness (10%)</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>No future-dated or long-expired events</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Event age distribution + future-dating check</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>Lowers DQI</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>dqi.timeliness</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>feed-quality-scorer.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>2. Feed quality (DQI)</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Usability (5%)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Contact info, restrictions, work-zone type present</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Share of events with actionable detail</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Lowers DQI</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>dqi.usability</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>feed-quality-scorer.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>2. Feed quality (DQI)</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Composite + grade</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>One comparable number per state feed</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Weighted mean of the 7 dimensions (weights sum to 1.0) -&gt; letter grade A-F</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>Published on the state report cards</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>dqi.overall / grade</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>feed-quality-scorer.js, report-card-service.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>3. Event confidence</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Completeness (35%)</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Per-EVENT (not per-feed) trustworthiness: are the critical fields there</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>id, eventType, start time, finite non-zero lat/lng, and the rest of the critical field set</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Lowers the event's 0-100 score</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>confidence.score</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>event-confidence.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>3. Event confidence</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Geospatial precision (15%)</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Point coordinates AND real linestring geometry present</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Both lat/lng and a LineString score full credit</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>Lowers score</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>confidence.score</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>event-confidence.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>3. Event confidence</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Temporal validity (20%)</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Has a start, has an end, is not stale</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>startTime present, end time present, age within bounds</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Lowers score</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>confidence.score</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>event-confidence.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>3. Event confidence</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Description quality (15%)</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>The narrative is specific, not boilerplate</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Length / specificity heuristic on the description</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>Lowers score</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>confidence.score</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>event-confidence.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>3. Event confidence</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Verification (15%)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>DOT operator comments corroborate the record</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Presence of corroborating operator narrative</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Lowers score</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>confidence.score</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>event-confidence.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>3. Event confidence</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Level banding</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Score becomes an operator-facing label</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>VERIFIED &gt;= 85, HIGH 70-84, MEDIUM 50-69, LOW 30-49, UNVERIFIED &lt; 30</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>Drives downstream filtering and display</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>confidence.level</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>event-confidence.js levelFromScore</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>4. Validator - DEVICE</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Gate 1: route</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>The arrow board / portable DMS is on the same route as the zone</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Device route must equal the zone's normalized route. A route-LESS device is allowed through on the other gates but starts at 30 base credit instead of 40</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Return null - not a match</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>x_cwz_connected</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>device-workzone-matcher.js scoreMatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>4. Validator - DEVICE</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Gate 2: carriageway</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>The device is not on the opposite side of a divided highway</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Same direction = +25; either side BOTH = +12; opposite = reject; unknown on either side = neutral (0, no reject)</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>Opposite carriageway -&gt; reject</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>x_cwz_connected</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>device-workzone-matcher.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>4. Validator - DEVICE</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Gate 3: proximity</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>The device is close enough to plausibly belong to the zone</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Distance to the zone geometry (snapped onto the line, or to the point) must be &lt;= 1600 m (~1 mi). Spatial credit = 25 * (1 - d/1600). &lt;= 150 m counts as effectively on the zone</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Beyond 1600 m -&gt; reject</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>x_connected_devices[].distanceM</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>device-workzone-matcher.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>4. Validator - DEVICE</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Gate 4: upstream (Field Escort rule)</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>The board sits UPSTREAM of the zone in the served travel direction - traffic has not already passed it</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>isUpstream() against the matched reference point. Skipped when the device is alongside the zone or direction is unknown/BOTH</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>Downstream -&gt; reject (it belongs to a different zone)</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>reasons[]</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>device-workzone-matcher.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>4. Validator - DEVICE</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Temporal</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>The device reported recently and inside the zone's active window</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Fresh = reported within 2 h (+5). Also checks the report timestamp falls between event start and end</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Stale still matches but scores 5 lower</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>device-workzone-matcher.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>4. Validator - DEVICE</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Deployment state</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>The board is actually ON, not blank / in transit</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>mode.displaying true (arrow/chevron/caution pattern) = +5</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>An off board can match but never AUTO-links (requireOnForAuto)</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>mode.displaying</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>device-workzone-matcher.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>4. Validator - DEVICE</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Scoring + banding</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Confidence is an honest number; questionable links go to a human</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>confidence = (40 if route known else 30) + dir + spatial + temporal + deploy. &gt;= 75 auto-link; 60-74 review queue; &lt; 60 no link. 'off' or &gt; 800 m block AUTO without lowering the score</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Below 60 no link; 60-74 surfaced for confirmation</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>x_connected_confidence</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>device-workzone-matcher.js DEFAULTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>4. Validator - DEVICE</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Independent post-check</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>The auto-links are audited using signals the matcher did NOT use</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Self-location parsed out of the device NAME ('SS2426 - I-35 NB @ MM 71.6') vs the feed's Route/Direction fields; message-vs-zone-type clash (the rest-area case); temporal; far / 'dir both' downgrades</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>Link downgraded and surfaced in the validation panel</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>validation flags</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>device-validation.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>4. Validator - CAMERA</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Match (free, no network)</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>There is a camera that could plausibly see the zone</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Nearest camera on the SAME interstate within 1500 m</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>No camera -&gt; no camera check is attempted</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>x_camera_id</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>camera-validation.js matchCamera</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>4. Validator - CAMERA</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Active-now gate</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Do not spend a vision call on a zone WZDx says is not running</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>isActiveNow(): now between start and end. null (no start date) also skips</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>Skipped, no cost</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>camera-validation.js isActiveNow</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>4. Validator - CAMERA</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Vision inference</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Temporary traffic control is physically deployed, not stored</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>ONE inference on the still snapshot returning {work_zone, deployed, staged_only, devices[arrow-board,cones,barrels,drums,signs,workers,tma], confidence}. Only DEPLOYED counts - staged/stored cones do not</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>No detection = soft negative (proximity is not line-of-sight; most feeds have no PTZ/heading)</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>x_camera_verified, x_camera_detected</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>camera-validation.js detect</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>4. Validator - CAMERA</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Cost controls</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Vision spend cannot run away</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Gated on a vision key being set (otherwise available:false, $0); per-snapshot-URL cache TTL 10 min; on-demand only, never in a timer or the shared refresh; cheapest model, tiny token budget; max 25 zones per scan</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>Silently unavailable rather than billing</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>camera-validation.js, camera-scan.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t>4. Validator - CAMERA</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Check-count policy</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>A closure is never re-billed indefinitely</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Check #1 only within 90 min of start. If it sees nothing, ONE follow-up after 30 min. Hard cap 2 vision checks per closure ever. A non-detection while vision is off does NOT consume a check</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Ledger enforces the cap across restarts</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>camera_check_ledger.checks</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>camera-scan.js, camera-check-ledger.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>4. Validator - CAMERA</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Removal detection (daily)</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>A multi-day zone that is actually finished stops being elevated even if WZDx still lists it</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Confirmed multi-day closures get one check per 24 h; traffic control gone -&gt; tc_removed. This is the ONLY validator that can take verification away</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>Zone drops out of the verified set</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>tc_removed</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>camera-check-ledger.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="21" t="inlineStr">
+        <is>
+          <t>4. Validator - PROBE (TomTom)</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Category filter</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Only genuine work-zone incidents count as corroboration</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>iconCategory in {7 lane closed, 8 road closed, 9 road works}; lat/lon finite</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Other incident types ignored</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>tomtom-corroboration.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="inlineStr">
+        <is>
+          <t>4. Validator - PROBE (TomTom)</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Spatial + route match</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>The independent incident is at the same place on the same road</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Same interstate, within 1500 m (maxM default)</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>No stamp applied</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>x_tomtom_corroborated</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>tomtom-corroboration.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="inlineStr">
+        <is>
+          <t>4. Validator - PROBE (TomTom)</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Independence + cost</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>This is a genuinely non-DOT opinion, obtained cheaply</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>TomTom's own probe network, not the state that published the zone. Reuses the already-cached incident set - zero extra API calls in the corroborator. Upstream fetch is budget- and rate-capped with a circuit breaker</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Absence never demotes a zone</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>x_tomtom_corroborated</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>tomtom-corroboration.js, tomtom-incidents.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>4. Validator - DMS</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Message content (strong)</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>The sign genuinely states roadwork or a closure</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>WZ_STRONG regex: ROAD WORK, WORK ZONE, LANE CLOSED, &lt;n&gt; LANES CLOSED, SHOULDER CLOSED/WORK, ROAD CLOSED, CLOSED AT/AHEAD/&lt;day&gt;, RAMP CLOSED, DETOUR, CONSTRUCTION, PAVING, MILLING, BRIDGE WORK, WORK AHEAD</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>No match -&gt; not evidence</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>x_dms_corroborated</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>dms-corroboration.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="21" t="inlineStr">
+        <is>
+          <t>4. Validator - DMS</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Message content (exclusions)</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>The unrelated messages a board cycles through are never counted</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>WZ_EXCLUDE regex rejects Amber/Silver/Blue alerts, seat-belt / drive-sober / phone-down / move-over campaigns, travel times and '&lt;n&gt; MIN', weather (wind, fog, snow, ice), crashes and disabled vehicles, game-day traffic, election notices</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Rejected even if a STRONG token also appears</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>dms-corroboration.js isWorkZoneMsg</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="inlineStr">
+        <is>
+          <t>4. Validator - DMS</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Weak-token removal</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Bare tokens that also appear in incident and generic messages do not qualify</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Deliberately dropped from the old rule: a lone CLOSED, MERGE, WORKERS, REDUCED SPEED, EXPECT DELAY</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>Requires a specific phrase instead</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>dms-corroboration.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="21" t="inlineStr">
+        <is>
+          <t>4. Validator - DMS</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Spatial + route match</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>The sign is near the zone, on the same road when known</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Same interstate when known, within a few miles; zone must be active now</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>No stamp applied</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>x_dms_corroborated</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>dms-corroboration.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="22" t="inlineStr">
+        <is>
+          <t>4. Validator - DMS</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Independence</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>A human operator in a different system posted this</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>DMS text is authored by an operator, not exported by the same automated WZDx pipeline being validated</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>Absence never demotes</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>x_dms_corroborated</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>dms-corroboration.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="23" t="inlineStr">
+        <is>
+          <t>5. Composition (CWZ 1.0)</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Positive-only semantics</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>A validator can only ever RAISE confidence</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>All four validators are positive-only. The single exception is the camera validator's daily removal check, which can withdraw verification</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Missing evidence is never treated as disproof</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>x_verification[]</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>cwz-roadevent-feed.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="24" t="inlineStr">
+        <is>
+          <t>5. Composition (CWZ 1.0)</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Source set</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>Which independent systems agree about this zone</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>x_verification collects any of: device, camera, tomtom, dms</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>Empty array = unverified</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>x_verification</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>cwz-roadevent-feed.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="23" t="inlineStr">
+        <is>
+          <t>5. Composition (CWZ 1.0)</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Corroboration count</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>How many INDEPENDENT sources agree - kept separate from how many devices are present</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>x_verification_count = number of distinct validators. x_connected_device_count is the physical device count and can be 0 while the zone is still corroborated by camera/TomTom/DMS</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>The two numbers are never conflated</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>x_verification_count</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>cwz-roadevent-feed.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="24" t="inlineStr">
+        <is>
+          <t>5. Composition (CWZ 1.0)</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Confidence tier</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Operator-facing banding of the corroboration count</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>&gt;= 2 sources = 'multi-source'; exactly 1 = 'single-source'; 0 = 'unverified'</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>Drives the multi-source filter on the elevated feed</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>x_confidence_tier</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>cwz-roadevent-feed.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="23" t="inlineStr">
+        <is>
+          <t>5. Composition (CWZ 1.0)</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Sticky accumulation</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Evidence accumulates rather than flickering between refreshes</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Verification flags persist once earned (camera removal excepted), so a zone does not oscillate as individual sources come and go</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>x_connection_status</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>validation-ledger.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="24" t="inlineStr">
+        <is>
+          <t>5. Composition (CWZ 1.0)</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>WZDx output</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>The result is a spec-valid feed others can consume</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>Emitted as WZDx v4.2 / CWZ 1.0 WorkZoneRoadEvent features with is_start_position_verified and the x_* evidence fields</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>full feature</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>cwz-roadevent-feed.js, cwz-device-feed.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>6. Monitoring</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Feed health</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>The upstream source itself is alive</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Is DMS_View returning data? how many devices are stale? fetch success history per feed</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Surfaced in the validation panel and availability dimension</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>device-validation.js, feed-tracking-service.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="20" t="inlineStr">
+        <is>
+          <t>6. Monitoring</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>How much of the network actually has independent evidence</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>Share of active work zones with a connected device / any verification source</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>Reported, not enforced</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>device-validation.js, coverage-gap-analyzer.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="19" t="inlineStr">
+        <is>
+          <t>6. Monitoring</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Lifecycle</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Events are retired when they should be</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Event lifecycle manager ages out and closes events; camera tc_removed feeds the same decision</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>Event leaves the active set</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>event-lifecycle-manager.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="20" t="inlineStr">
+        <is>
+          <t>6. Monitoring</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>Exceptions / stewardship</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>A human is told when something needs attention</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>Work-zone exceptions raised to stewards (WZ_STEWARDS) via WZ_NOTIFY_WEBHOOK</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>Notification</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>wz-exceptions.js</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G55"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/Corridor_Communicator_API_Inventory.xlsx
+++ b/docs/Corridor_Communicator_API_Inventory.xlsx
@@ -8,22 +8,24 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internal REST API" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Feed Registry" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External APIs Consumed" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Published Feeds" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Camera Sources" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DMS + Device Sources" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation Logic" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Pulled + How Used" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internal REST API" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Feed Registry" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External APIs Consumed" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Published Feeds" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Camera Sources" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DMS + Device Sources" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation Logic" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Internal REST API'!$A$1:$I$512</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'State Feed Registry'!$A$1:$G$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'External APIs Consumed'!$A$1:$G$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Published Feeds'!$A$1:$F$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Camera Sources'!$A$1:$H$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'DMS + Device Sources'!$A$1:$J$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Validation Logic'!$A$1:$G$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data Pulled + How Used'!$A$1:$I$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Internal REST API'!$A$1:$I$512</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'State Feed Registry'!$A$1:$G$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'External APIs Consumed'!$A$1:$G$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Published Feeds'!$A$1:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Camera Sources'!$A$1:$H$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'DMS + Device Sources'!$A$1:$J$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Validation Logic'!$A$1:$G$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -32,7 +34,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -90,6 +92,10 @@
       <b val="1"/>
       <color rgb="006B1F8C"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000F6B78"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -135,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -201,6 +207,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -568,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C123"/>
+  <dimension ref="A1:C126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2178,12 +2190,1791 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Data flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Data Pulled + How Used - every dataset ingested (36 across 24 domains): source, extracted fields, refresh cadence, storage, consumers, and which outbound feed it reaches</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="62" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>What we extract</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Refresh cadence</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Where it lands</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>How it is used</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Emitted in</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Implemented in</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Work zones</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>State work-zone events (WZDx v4.x / CWZ)</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>37 registered state feeds - see 'State Feed Registry'</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Event id, type, route, direction, start/end time, description, lanes affected, severity, geometry</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>On demand: 5-min cache, background refresh triggered at 4 min. No user-facing polling</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>eventsCache (in-process) + cached_events table with provenance, confidence_score, quality_flags, validation_status</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>The corridor map, /api/events, every validator's input set, DQI scoring, report cards</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>WZDx v4.2 feed, CWZ 1.0 RoadEvent feed, CIFS, TIM</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>backend_proxy_server.js, services/event-adapters.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Work zones</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Iowa lane-closure planning data</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Iowa DOT RoadClosures_public (AGOL, CORS-open)</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Planned closure geometry, route, dates</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>On demand when a builder opens</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Client-side in the builder (no backend hop)</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Conflict check in the CARS 511 request builder - warns when a new request overlaps a planned closure</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>frontend builders (self-contained)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Work zones</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Mobile / fast-refresh feeds (Field Escort)</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>purposebuiltsystems.github.io + registered plugin feeds</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Transient machine-published WZDx GeoJSON, expires_at</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Per-feed timer honoring plugin_data_feeds.refresh_interval (sub-hour)</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>plugin_data_feeds tables, UPSERT by machine id, expired rows pruned</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Adds mobile/short-duration zones the hourly CIFS poller misses</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Flows into /api/events downstream</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>services/mobile-feed-ingest.js (draft, inert until wired in)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Devices</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>DMS + arrow board / portable sign feeds</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>18 state feeds - see 'DMS + Device Sources'</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Device id, type, portable flag, route, direction, coordinates, displayed message, mode.displaying, last updated</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Refreshed alongside the event cache (~5 min); Iowa DMS_View cached 10 min</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>devicesCache (roster + auto-links + review queue)</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Device-to-work-zone auto-association (the strongest validator); DMS text corroboration; validation panel</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>CWZ 1.0 Device feed; x_cwz_connected / x_connected_devices on the RoadEvent feed</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>services/device-adapters.js, device-workzone-matcher.js, dms-corroboration.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>Cameras</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Traffic camera inventory + still snapshots</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>15 state networks - see 'Camera Sources' (21,941 cameras)</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Camera id, route, direction, milepost, coordinates, current still-image URL</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Inventory cached 30 min (locations are static); snapshots fetched only when a check is due</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>In-process camera cache; per-closure state in camera_check_ledger</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Camera-vision validation of whether traffic control is physically deployed; the daily removal check</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>x_camera_verified / x_camera_detected / x_camera_url on the CWZ feed</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>services/camera-adapters.js, camera-validation.js, camera-scan.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>Cameras</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Vision inference results</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Anthropic Messages API (or OpenAI / a self-hosted YOLO endpoint)</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>{work_zone, deployed, staged_only, devices[arrow-board, cones, barrels, drums, signs, workers, tma], confidence}</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>One inference per due closure, max 2 per closure ever, 10-min per-snapshot cache, 25 zones per scan</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Elevation flags on the event + a training log (VISION_TRAINING_LOG on the Railway /data volume)</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Confirms deployed (not stored) traffic control; feeds the removal state machine</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>x_camera_* fields</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>services/camera-validation.js, vision-training-log.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>Probe traffic</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>TomTom traffic incidents</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>TomTom Traffic Incident Details v5</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Incident id, iconCategory (7 lane closed / 8 road closed / 9 road works), lat/lon, description</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Lazy: only polled when the layer is requested. Corridor TTL 45 min, zone-tile TTL 6 h (~800 req/day, self-capped at 2500)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>tomtomCache + tomtomZoneCache; validations banked in the validation ledger</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Independent non-DOT corroboration of work zones; the DOT-vs-consumer-nav deviation view</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>x_tomtom_corroborated</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>services/tomtom-incidents.js, tomtom-corroboration.js, tomtom-deviation.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>Weather</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>NWS active CAP alerts</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>https://api.weather.gov/alerts/active</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Alert id, event label, severity, urgency, certainty, areaDesc, derived state codes, geometry</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>On demand, cached</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>In-process cache</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Weather hazards on the corridor map; the single biggest gap-filler for the ~17 states with no public WZDx/511 feed; IPAWS context</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>/api/weather-alerts</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>services/nws-alerts.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>FARS historical crash records</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>NHTSA annual national CSV bundles (static.nhtsa.gov)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>accident.csv LATITUDE/LONGITUD, WRK_ZONE (0-4); vehicle.csv BODY_TYP large-truck range + MCARR_ID</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Monthly - scheduler runs on the 2nd at 4:00 AM. (The live CrashAPI 403s datacenter IPs, hence bulk files)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>crash_records in the PostGIS Postgres via crashDb (not the SQLite db)</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Crash analytics: commercial-vehicle involvement and work-zone crashes clipped to within CRASH_CORRIDOR_BUFFER_MILES of the I-80 / I-35 polyline</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>/api/crashes/*</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>services/crash-data-service.js, scheduler-service.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Emergency</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>IPAWS / WEA alerting</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Iowa DOT IPAWS policy; 511ia.org + OSRM for geometry</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Qualifying closures (&gt;= 4 h or imminent danger), geofence polygons, CAP-XML payloads</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Evaluated against the active event set</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>ipaws_alert_log / ipaws_active_alerts (+ _lite variants)</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Automatic WEA qualification, precision geofence with population masking, multilingual CAP (EN/ES/Lao/Somali), audit log</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>/api/ipaws/* (33 endpoints)</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>services/ipaws-alert-service.js, ipaws-alert-service-lite.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Census population + urban extent</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Census decennial PL, TIGERweb, OSM Overpass/Nominatim, Google Earth Engine (LandScan)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Block-level population, urban area boundaries, POI/road context</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>On demand per geofence</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Computed per request; cached</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Population inside an IPAWS geofence, exclusion of populated/urban areas, real-time population-impact estimates for alert targeting</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>/api/population/*</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>services/population-density-service.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Truck parking</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>MAASTO TPIMS static + dynamic</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>8 Midwest DOTs via truckparking.travelmidwest.com (TPIMS V2.2), plus MnDOT IRIS, WisDOT transportal, TRIMARC</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Static: siteId, lat/lng, name, capacity, amenities. Dynamic: reportedAvailable, trend, open status. Joined on siteId</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Every 30 min (server timer)</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>parking_facilities, parking_availability</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Live truck-parking availability on the map; ground truth for the prediction model</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>/api/parking/* (28 endpoints), /api/maasto-tpims</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>services/maasto-tpims.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Truck parking</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Iowa rest-area camera snapshots</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>atmsqf.iowadot.gov/snapshots/Public/RestAreas/*.jpg</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Still images of rest-area entrances, exits and truck-parking aprons</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>On demand</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Not stored; read at request time</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Visual occupancy check and calibration against the prediction model</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>/api/parking/*</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>truck_parking_service.js, services/parking-calibration-service.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Truck parking</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Historical occupancy patterns</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Derived internally from observations + bundled seed data</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Hour-of-week occupancy curves per facility, ground-truth observations, prediction accuracy</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>Recomputed on demand; seeded at startup from bundled_data/truck_parking_patterns.json</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>parking_patterns, parking_occupancy_patterns, parking_observations, parking_ground_truth_observations, parking_prediction_accuracy</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>Availability prediction where no live sensor exists; accuracy scoring of the predictions</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>/api/parking/*</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>parking_prediction.js, truck_parking_service.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>Geometry</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>ARNOLD linear-referenced road network</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>FHWA/BTS geo.dot.gov ARNOLD_&lt;ST&gt;_&lt;YEAR&gt; FeatureServers (48 mainland states)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Route polylines by route_id + milepost range</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>On demand per event needing geometry</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Enriched onto the event; osrm_geometry_cache / interstate_geometries</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Turns route+milepost work zones into real road-following linework instead of straight lines</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Geometry on every outbound feed</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>services/arnold-geometry-service.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>Geometry</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>State centerlines + milepost layers</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Caltrans SHN, TxDOT Roadways/Mile Markers, NJ, IL, MO, WY, MA, CO ArcGIS services</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>State-native route ids and milepost points</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>On demand</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>Enriched onto the event</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>State-centerline-first geometry - fixes the CA/TX case where ARNOLD route_id schemas do not match (CA uses name-composites, not '0005')</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>Geometry on outbound feeds</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>services/state-centerline-service.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>Geometry</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Iowa RAMS reference posts</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>gis.iowadot.gov Reference_Post_View</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Route, reference-post chainage</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>On demand, cached</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Iowa geometry cache (expired rows cleaned hourly)</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Chainage-based linear position for device-to-work-zone matching, rather than raw straight-line distance</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>services/rams-chainage.js, iowa-geometry-service.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>Routing</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>OSRM driving routes</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>router.project-osrm.org /route/v1/driving</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Route geometry (GeoJSON overview), distance, duration</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>On demand, queued and rate-limited</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>osrm_geometry_cache table (persisted so a route is never re-fetched)</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>Detour and diversion-route generation, travel-time estimates, IPAWS geofence shaping</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>/api/diversion-routes/*, /api/osrm/*</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>backend_proxy_server.js, services/ipaws-alert-service.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Freight</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>National Bridge Inventory</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>NTAD NBI FeatureServer (services.arcgis.com/xOi1kZaI0eWDREZv)</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Structure location, carries/crosses road names, vertical underclearance, NBI inspection date</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>On demand per work zone</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>bridge_clearances, bridge_clearance_warnings, bridge_restrictions</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>OSOW clearance layer; annotates any work zone with the structures the route passes UNDER (only those actually restrict you) plus a construction-proximity staleness flag</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>Clearance fields on the DTCD / CWZ feed, /api/bridge-clearances/*</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>services/nbi-clearance.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>Freight</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>CBP border wait times</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>https://bwt.cbp.gov/api/waittimes</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>port_number, port_name, crossing_name, border, hours, lane wait times (+ a locally maintained coordinate lookup, since CBP returns no lat/lng)</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>On demand</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>In-process cache</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>Border crossings as map markers with live waits for freight corridor views; wait-time notifications</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>/api/border-wait-times, /api/border-notifications/*</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>services/border-wait-times.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>Freight</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>State OSOW regulations + corridor regulations</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Curated / seeded reference content</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Per-state oversize-overweight rules, NASCO corridor regulations</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Seeded once at startup if empty (idempotent - manual edits survive redeploy)</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>corridor_regulations, state OSOW tables</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Permit and routing guidance in the freight views</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>/api/state-osow-regulations/*, /api/corridor-regulations</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>backend_proxy_server.js, scripts/seed_corridor_regulations_if_empty.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Major events (concerts, games)</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Ticketmaster Discovery v2; PredictHQ as the alternate</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Event name, venue, coordinates, start time, expected attendance</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>Cached 6 h; gated on the API key being set (Ticketmaster key not set yet)</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>majorEventsCache</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>Demand-surge alerts near the corridor - warns when an event will load the same segment as a work zone</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>/api/major-events</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>services/ticketmaster-service.js, predicthq-service.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>ITS assets</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>ITS equipment + RSU inventory</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>NTAD RSU Deployment Locations; internally maintained equipment records</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Device type, location, status, health telemetry</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>On demand</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>its_equipment (3,149 rows), rsu_inventory, rsu_health, sensor_inventory (925), sensor_health, sensor_health_telemetry, device_health_snapshots</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>V2X / connected-vehicle layer, asset-health monitoring, predictive maintenance, network topology</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>/api/its-equipment/* (18), /api/v2x/*, /api/asset-health/*, /api/network/*</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>services/asset-health-monitor.js, predictive-maintenance-ai.js, device-health-store.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>Digital infra</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>BIM / IFC models and CADD drawings</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>User-uploaded IFC, DXF and CADD files (+ buildingSMART schema references)</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>IFC entities, DXF layers and entities, extracted geometry</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>On upload</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>ifc_models, cadd_models, cadd_layers, cadd_entities, infrastructure_elements, infrastructure_standards, infrastructure_gaps</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>Digital-infrastructure inventory, standards crosswalk, gap analysis, GIS export of CADD content</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>/api/digital-infrastructure/* (12), /api/bim/*, /api/cadd/* (9)</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>services/cadd-processor.js, cadd-gis-exporter.js, dxf-extractor.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Imagery</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Aerial overlays</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>User-uploaded GeoTIFF / imagery</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Georeferenced raster tiles and bounds</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>On upload</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>S3-compatible object store (S3_ENDPOINT) + aerial_overlays metadata</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Aerial imagery overlay on the corridor map for planning and review</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>/api/aerial-overlays/*</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>services/aerial-overlays.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>Grants</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Federal funding opportunities</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Grants.gov search2 + fetchOpportunity</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Opportunity number, title, agency, dates, eligibility, award ceiling - filtered by an ITS/digital-infrastructure keyword set (WZDx, connected corridors, CV/CAV, ITS deployment), NOT general transportation</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>On demand</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>Grants tables</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>Grant discovery, the proposal analyzer, and the grant package builder</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>/api/grants/* (23), /api/funding-opportunities/*</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>services/grants-service.js, compliance-analyzer.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Feed fetch history and outcomes</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Recorded internally on every upstream fetch</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Success/failure, latency, record counts, per-feed timestamps</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Written on each fetch</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>quality_history, api_usage_logs, api_access_log, rate_limit_log</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>The Availability dimension of the DQI, feed outage detection, the state report cards</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>/api/data-quality/* (23), /api/reports/*, /api/quality/*</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>services/feed-tracking-service.js, feed-quality-scorer.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Validation evidence ledger</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Produced by the four validators</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Per-zone verification sources, timestamps, confidence, sticky accumulation state</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>On each validation pass</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>validation ledger tables + camera_check_ledger</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>Keeps verification from flickering between refreshes; supplies x_verification / x_confidence_tier</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>CWZ 1.0 feeds, /api/wz/*, /api/confidence/*</t>
+        </is>
+      </c>
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t>services/validation-ledger.js, camera-check-ledger.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Coalition calendar, messages, community posts</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>User-generated in the platform</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Events, RSVPs, action items, artifacts, threads, reactions, biweekly reports</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>calendar_events, calendar_rsvps, calendar_action_items, calendar_artifacts, message_threads, message_reactions, alert_notifications</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>The I-80 coalition calendar, inter-state messaging, community board, biweekly reporting</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>/api/calendar/* (16), /api/messages/*, /api/community/*, /api/biweekly-reports/*</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>calendar-api.js, backend_proxy_server.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Vendor uploads</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Truck-parking and other vendor submissions</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Uploaded facility and availability data with provenance</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>On upload</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>Vendor tables + parking tables</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>Lets vendors contribute parking data where no state feed exists</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>/api/vendors/* (12)</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>vendor-upload-service.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Outbound alert delivery</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>SendGrid, Twilio, Slack, Microsoft Teams, ServiceNow</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Rendered alert payloads (email, SMS, webhook cards, incident tickets)</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>High-severity event check every 5 min; daily digest</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>alert_history, alert_rules, alerts</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>Routing high-severity events and asset-health exceptions to the right people and systems</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>services/notification-service.js, email-service.js, daily-digest.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>LLM analysis and assistant</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Anthropic Messages API / OpenAI Chat Completions</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Prompts built from corridor data; structured JSON responses</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>On demand only - never on a shared or startup path</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>chat_conversations</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>The corridor briefing, NASCO corridor AI analysis, grant proposal analysis, the in-app assistant, and the custom-GPT action surface</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>/api/chat/*, /api/chatgpt/* (14), /api/corridor-briefing, /api/nasco-corridor-ai-analysis</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>backend_proxy_server.js, ml-integrations.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Prediction models</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Internal ML service (ML_SERVICE_URL, ml-service/)</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Feature vectors from parking, event and traffic history</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>On demand</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>Model outputs cached alongside the source tables</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Parking availability prediction, predictive maintenance, traffic-impact analysis</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>/api/ml/* (10), /api/predictive/*, /api/predictive-maintenance/*</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>ml-integrations.js, parking_prediction.js, traffic_impact_analyzer.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Interstate polylines (I-80, I-35)</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Loaded from PostGIS at startup</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Directional centerlines per corridor (i-80-eb/wb, i-35-nb/sb)</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>Once at startup</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>interstatePolylinesCache, interstate_geometries</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>Corridor clipping for crash data, geometry snapping, corridor analytics and the map base</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I35" s="8" t="inlineStr">
+        <is>
+          <t>backend_proxy_server.js getCorridorLine</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Interchanges and route restrictions</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Curated / admin-maintained</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Interchange locations, route restrictions</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Admin edits</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>interchanges, route_restrictions</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Detour feasibility, diversion routing, traveler information</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>/api/interchanges, /api/admin/interchanges</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>backend_proxy_server.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Users, API keys, admin tokens</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Accounts, roles, hashed credentials, issued keys and their usage</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>users, api_keys, admin_tokens, api_access_log</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>Authentication, state-level access control, API key issuance and rate limiting</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>/api/users/* (12), /api/admin/* (32)</t>
+        </is>
+      </c>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>backend_proxy_server.js</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I37"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -24043,7 +25834,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -25473,7 +27264,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -27199,7 +28990,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -27510,7 +29301,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -28165,7 +29956,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -29080,7 +30871,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/Corridor_Communicator_API_Inventory.xlsx
+++ b/docs/Corridor_Communicator_API_Inventory.xlsx
@@ -11,21 +11,23 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Pulled + How Used" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internal REST API" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Feed Registry" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External APIs Consumed" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Published Feeds" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Camera Sources" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DMS + Device Sources" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation Logic" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Coverage Matrix" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External APIs Consumed" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Published Feeds" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Camera Sources" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DMS + Device Sources" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation Logic" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data Pulled + How Used'!$A$1:$I$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Internal REST API'!$A$1:$I$512</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'State Feed Registry'!$A$1:$G$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'External APIs Consumed'!$A$1:$G$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Published Feeds'!$A$1:$F$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Camera Sources'!$A$1:$H$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'DMS + Device Sources'!$A$1:$J$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Validation Logic'!$A$1:$G$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'State Feed Registry'!$A$1:$H$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'State Coverage Matrix'!$A$1:$K$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'External APIs Consumed'!$A$1:$G$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Published Feeds'!$A$1:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Camera Sources'!$A$1:$H$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'DMS + Device Sources'!$A$1:$J$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Validation Logic'!$A$1:$G$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -97,7 +99,7 @@
       <color rgb="000F6B78"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -112,6 +114,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F5FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDECEA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF6E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -141,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -213,6 +225,30 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -580,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C126"/>
+  <dimension ref="A1:C133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -598,7 +634,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-03 from the working tree (backend_proxy_server.js, ml-integrations.js, services/, states.db)</t>
+          <t>Generated 2026-09-03. Endpoints from the working tree (backend_proxy_server.js, ml-integrations.js, services/). State feed registry read LIVE from production /api/states/list - the local states.db is stale and differs. Camera and device counts are live pulls from each upstream feed.</t>
         </is>
       </c>
     </row>
@@ -639,12 +675,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Registered state feeds (states.db)</t>
+          <t>Registered feeds (production registry)</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
         <v>37</v>
       </c>
+      <c r="C8">
+        <f> 33 US states + DTCD, Quebec City, Austin TX, and a 2nd Iowa feed</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2204,7 +2244,2108 @@
         </is>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>State coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>State Coverage Matrix - all 50 states + DC, showing which channels reach each one</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>33 states have a work-zone event feed; 15 have cameras; 9 have a live DMS/device feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Maine has cameras + a portable-DMS feed but NO event feed - the closest state to full coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>17 (16 states + DC) are reached only by nationwide NWS weather alerts: AL AK AR CT DC MI MT NH ND OR RI SC SD TN VT WV WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>8 more device feeds unlock with a free 511 key: UT LA AZ NC NJ WI NV ID</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="74" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>What it validates</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Rule / threshold as coded</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>On fail</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Output field</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Implemented in</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>0. Ingest / normalize</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Route normalization</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Free-text route strings from 37 different feeds resolve to one canonical route id</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Regex ladder: I-nnn first (ramp strings embed it), then US-nnn, then &lt;ST&gt;-nnn. 'I 380', 'I-380', 'RAMP: I 80E TO 100TH ST' all -&gt; 'I-380'/'I-80'</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Returns null -&gt; the record cannot be route-matched and is skipped by the matcher</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>route / rawRoute</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>device-workzone-matcher.js normalizeRoute</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>0. Ingest / normalize</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Direction normalization</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Carriageway direction is one of N/S/E/W/BOTH</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>First letter after uppercasing; 'Both'/'B' -&gt; BOTH; anything else -&gt; null (neutral, not a reject)</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>null = unknown, treated as neutral rather than a mismatch</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>direction</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>device-workzone-matcher.js normalizeDir</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>0. Ingest / normalize</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Coordinate sanity</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Lat/lon are real and not a null-island artifact</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Both finite, not (0,0), |lat| &lt;= 90, |lon| &lt;= 180</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Record dropped at normalize()</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>coordinates</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>device-adapters.js normalize</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>1. Geometry</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Missing content</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Event has geometry and some human content</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>No geometry -&gt; drop. Empty description AND empty location -&gt; drop</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Event filtered out entirely</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>geometry-validator.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>1. Geometry</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Fallback-geometry rejection</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Geometry is not an interpolated straight line masquerading as road shape</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>geometrySource in ('straight_line','straight') -&gt; drop</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Event filtered out</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>geometry-validator.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>1. Geometry</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>2-point LineString collapse</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>A 2-point line carries no road shape, so it must not render as a road</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>LineString with exactly 2 coordinates -&gt; converted to a Point at the midpoint</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Downgraded to a marker, not dropped</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>_geometryFixed</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>geometry-validator.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>1. Geometry</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Curvature test (long lines)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>A very long 'closure' line actually follows the road rather than cutting across it</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>chord &gt; 50 mi AND path length / chord &lt; 1.05 (under 5% curvature) -&gt; drop</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Event filtered out</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>geometry-validator.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>1. Geometry</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Type validity</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Point/LineString/Polygon/Multi* are structurally well formed</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Point needs 2 coords; LineString &gt;= 2; Polygon outer ring &gt;= 4; Multi* non-empty; unknown type -&gt; drop</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Event filtered out</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>geometry-validator.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>2. Feed quality (DQI)</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Completeness (20%)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Required WZDx fields are actually populated across the feed</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Share of events carrying end time, description, geometry, severity, lanes affected</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Lowers the feed's DQI and letter grade</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>dqi.completeness</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>feed-quality-scorer.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>2. Feed quality (DQI)</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Freshness (15%)</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>The feed is being updated and events are not stale</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Update latency + stale-event share</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Lowers DQI</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>dqi.freshness</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>feed-quality-scorer.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>2. Feed quality (DQI)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Accuracy (20%)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Geometry validates and the payload matches schema</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Geometry validation pass rate + schema compliance</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Lowers DQI</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>dqi.accuracy</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>feed-quality-scorer.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>2. Feed quality (DQI)</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Availability (15%)</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>The endpoint answers reliably</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Fetch success / failure history per feed key</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Lowers DQI; feeds an outage signal</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>dqi.availability</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>feed-quality-scorer.js + feed-tracking-service.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>2. Feed quality (DQI)</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Standardization (15%)</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>WZDx compliance, valid event types, ITIS codes</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Share of events using spec-valid enumerations</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Lowers DQI</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>dqi.standardization</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>feed-quality-scorer.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>2. Feed quality (DQI)</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Timeliness (10%)</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>No future-dated or long-expired events</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Event age distribution + future-dating check</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>Lowers DQI</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>dqi.timeliness</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>feed-quality-scorer.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>2. Feed quality (DQI)</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Usability (5%)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Contact info, restrictions, work-zone type present</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Share of events with actionable detail</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Lowers DQI</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>dqi.usability</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>feed-quality-scorer.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>2. Feed quality (DQI)</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Composite + grade</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>One comparable number per state feed</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Weighted mean of the 7 dimensions (weights sum to 1.0) -&gt; letter grade A-F</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>Published on the state report cards</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>dqi.overall / grade</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>feed-quality-scorer.js, report-card-service.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>3. Event confidence</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Completeness (35%)</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Per-EVENT (not per-feed) trustworthiness: are the critical fields there</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>id, eventType, start time, finite non-zero lat/lng, and the rest of the critical field set</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Lowers the event's 0-100 score</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>confidence.score</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>event-confidence.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>3. Event confidence</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Geospatial precision (15%)</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Point coordinates AND real linestring geometry present</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Both lat/lng and a LineString score full credit</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>Lowers score</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>confidence.score</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>event-confidence.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>3. Event confidence</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Temporal validity (20%)</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Has a start, has an end, is not stale</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>startTime present, end time present, age within bounds</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Lowers score</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>confidence.score</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>event-confidence.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>3. Event confidence</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Description quality (15%)</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>The narrative is specific, not boilerplate</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Length / specificity heuristic on the description</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>Lowers score</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>confidence.score</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>event-confidence.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>3. Event confidence</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Verification (15%)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>DOT operator comments corroborate the record</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Presence of corroborating operator narrative</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Lowers score</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>confidence.score</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>event-confidence.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>3. Event confidence</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Level banding</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Score becomes an operator-facing label</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>VERIFIED &gt;= 85, HIGH 70-84, MEDIUM 50-69, LOW 30-49, UNVERIFIED &lt; 30</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>Drives downstream filtering and display</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>confidence.level</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>event-confidence.js levelFromScore</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>4. Validator - DEVICE</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Gate 1: route</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>The arrow board / portable DMS is on the same route as the zone</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Device route must equal the zone's normalized route. A route-LESS device is allowed through on the other gates but starts at 30 base credit instead of 40</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Return null - not a match</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>x_cwz_connected</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>device-workzone-matcher.js scoreMatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>4. Validator - DEVICE</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Gate 2: carriageway</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>The device is not on the opposite side of a divided highway</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Same direction = +25; either side BOTH = +12; opposite = reject; unknown on either side = neutral (0, no reject)</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>Opposite carriageway -&gt; reject</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>x_cwz_connected</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>device-workzone-matcher.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>4. Validator - DEVICE</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Gate 3: proximity</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>The device is close enough to plausibly belong to the zone</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Distance to the zone geometry (snapped onto the line, or to the point) must be &lt;= 1600 m (~1 mi). Spatial credit = 25 * (1 - d/1600). &lt;= 150 m counts as effectively on the zone</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Beyond 1600 m -&gt; reject</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>x_connected_devices[].distanceM</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>device-workzone-matcher.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>4. Validator - DEVICE</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Gate 4: upstream (Field Escort rule)</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>The board sits UPSTREAM of the zone in the served travel direction - traffic has not already passed it</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>isUpstream() against the matched reference point. Skipped when the device is alongside the zone or direction is unknown/BOTH</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>Downstream -&gt; reject (it belongs to a different zone)</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>reasons[]</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>device-workzone-matcher.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>4. Validator - DEVICE</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Temporal</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>The device reported recently and inside the zone's active window</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Fresh = reported within 2 h (+5). Also checks the report timestamp falls between event start and end</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Stale still matches but scores 5 lower</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>device-workzone-matcher.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>4. Validator - DEVICE</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Deployment state</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>The board is actually ON, not blank / in transit</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>mode.displaying true (arrow/chevron/caution pattern) = +5</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>An off board can match but never AUTO-links (requireOnForAuto)</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>mode.displaying</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>device-workzone-matcher.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>4. Validator - DEVICE</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Scoring + banding</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Confidence is an honest number; questionable links go to a human</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>confidence = (40 if route known else 30) + dir + spatial + temporal + deploy. &gt;= 75 auto-link; 60-74 review queue; &lt; 60 no link. 'off' or &gt; 800 m block AUTO without lowering the score</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Below 60 no link; 60-74 surfaced for confirmation</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>x_connected_confidence</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>device-workzone-matcher.js DEFAULTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>4. Validator - DEVICE</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Independent post-check</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>The auto-links are audited using signals the matcher did NOT use</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Self-location parsed out of the device NAME ('SS2426 - I-35 NB @ MM 71.6') vs the feed's Route/Direction fields; message-vs-zone-type clash (the rest-area case); temporal; far / 'dir both' downgrades</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>Link downgraded and surfaced in the validation panel</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>validation flags</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>device-validation.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>4. Validator - CAMERA</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Match (free, no network)</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>There is a camera that could plausibly see the zone</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Nearest camera on the SAME interstate within 1500 m</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>No camera -&gt; no camera check is attempted</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>x_camera_id</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>camera-validation.js matchCamera</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>4. Validator - CAMERA</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Active-now gate</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Do not spend a vision call on a zone WZDx says is not running</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>isActiveNow(): now between start and end. null (no start date) also skips</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>Skipped, no cost</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>camera-validation.js isActiveNow</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>4. Validator - CAMERA</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Vision inference</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Temporary traffic control is physically deployed, not stored</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>ONE inference on the still snapshot returning {work_zone, deployed, staged_only, devices[arrow-board,cones,barrels,drums,signs,workers,tma], confidence}. Only DEPLOYED counts - staged/stored cones do not</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>No detection = soft negative (proximity is not line-of-sight; most feeds have no PTZ/heading)</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>x_camera_verified, x_camera_detected</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>camera-validation.js detect</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>4. Validator - CAMERA</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Cost controls</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Vision spend cannot run away</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Gated on a vision key being set (otherwise available:false, $0); per-snapshot-URL cache TTL 10 min; on-demand only, never in a timer or the shared refresh; cheapest model, tiny token budget; max 25 zones per scan</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>Silently unavailable rather than billing</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>camera-validation.js, camera-scan.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t>4. Validator - CAMERA</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Check-count policy</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>A closure is never re-billed indefinitely</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Check #1 only within 90 min of start. If it sees nothing, ONE follow-up after 30 min. Hard cap 2 vision checks per closure ever. A non-detection while vision is off does NOT consume a check</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Ledger enforces the cap across restarts</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>camera_check_ledger.checks</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>camera-scan.js, camera-check-ledger.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>4. Validator - CAMERA</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Removal detection (daily)</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>A multi-day zone that is actually finished stops being elevated even if WZDx still lists it</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Confirmed multi-day closures get one check per 24 h; traffic control gone -&gt; tc_removed. This is the ONLY validator that can take verification away</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>Zone drops out of the verified set</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>tc_removed</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>camera-check-ledger.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="21" t="inlineStr">
+        <is>
+          <t>4. Validator - PROBE (TomTom)</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Category filter</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Only genuine work-zone incidents count as corroboration</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>iconCategory in {7 lane closed, 8 road closed, 9 road works}; lat/lon finite</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Other incident types ignored</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>tomtom-corroboration.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="inlineStr">
+        <is>
+          <t>4. Validator - PROBE (TomTom)</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Spatial + route match</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>The independent incident is at the same place on the same road</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Same interstate, within 1500 m (maxM default)</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>No stamp applied</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>x_tomtom_corroborated</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>tomtom-corroboration.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="inlineStr">
+        <is>
+          <t>4. Validator - PROBE (TomTom)</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Independence + cost</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>This is a genuinely non-DOT opinion, obtained cheaply</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>TomTom's own probe network, not the state that published the zone. Reuses the already-cached incident set - zero extra API calls in the corroborator. Upstream fetch is budget- and rate-capped with a circuit breaker</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Absence never demotes a zone</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>x_tomtom_corroborated</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>tomtom-corroboration.js, tomtom-incidents.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>4. Validator - DMS</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Message content (strong)</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>The sign genuinely states roadwork or a closure</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>WZ_STRONG regex: ROAD WORK, WORK ZONE, LANE CLOSED, &lt;n&gt; LANES CLOSED, SHOULDER CLOSED/WORK, ROAD CLOSED, CLOSED AT/AHEAD/&lt;day&gt;, RAMP CLOSED, DETOUR, CONSTRUCTION, PAVING, MILLING, BRIDGE WORK, WORK AHEAD</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>No match -&gt; not evidence</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>x_dms_corroborated</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>dms-corroboration.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="21" t="inlineStr">
+        <is>
+          <t>4. Validator - DMS</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Message content (exclusions)</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>The unrelated messages a board cycles through are never counted</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>WZ_EXCLUDE regex rejects Amber/Silver/Blue alerts, seat-belt / drive-sober / phone-down / move-over campaigns, travel times and '&lt;n&gt; MIN', weather (wind, fog, snow, ice), crashes and disabled vehicles, game-day traffic, election notices</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Rejected even if a STRONG token also appears</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>dms-corroboration.js isWorkZoneMsg</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="inlineStr">
+        <is>
+          <t>4. Validator - DMS</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Weak-token removal</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Bare tokens that also appear in incident and generic messages do not qualify</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Deliberately dropped from the old rule: a lone CLOSED, MERGE, WORKERS, REDUCED SPEED, EXPECT DELAY</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>Requires a specific phrase instead</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>dms-corroboration.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="21" t="inlineStr">
+        <is>
+          <t>4. Validator - DMS</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Spatial + route match</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>The sign is near the zone, on the same road when known</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Same interstate when known, within a few miles; zone must be active now</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>No stamp applied</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>x_dms_corroborated</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>dms-corroboration.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="22" t="inlineStr">
+        <is>
+          <t>4. Validator - DMS</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Independence</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>A human operator in a different system posted this</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>DMS text is authored by an operator, not exported by the same automated WZDx pipeline being validated</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>Absence never demotes</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>x_dms_corroborated</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>dms-corroboration.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="23" t="inlineStr">
+        <is>
+          <t>5. Composition (CWZ 1.0)</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Positive-only semantics</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>A validator can only ever RAISE confidence</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>All four validators are positive-only. The single exception is the camera validator's daily removal check, which can withdraw verification</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Missing evidence is never treated as disproof</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>x_verification[]</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>cwz-roadevent-feed.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="24" t="inlineStr">
+        <is>
+          <t>5. Composition (CWZ 1.0)</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Source set</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>Which independent systems agree about this zone</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>x_verification collects any of: device, camera, tomtom, dms</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>Empty array = unverified</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>x_verification</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>cwz-roadevent-feed.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="23" t="inlineStr">
+        <is>
+          <t>5. Composition (CWZ 1.0)</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Corroboration count</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>How many INDEPENDENT sources agree - kept separate from how many devices are present</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>x_verification_count = number of distinct validators. x_connected_device_count is the physical device count and can be 0 while the zone is still corroborated by camera/TomTom/DMS</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>The two numbers are never conflated</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>x_verification_count</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>cwz-roadevent-feed.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="24" t="inlineStr">
+        <is>
+          <t>5. Composition (CWZ 1.0)</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Confidence tier</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Operator-facing banding of the corroboration count</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>&gt;= 2 sources = 'multi-source'; exactly 1 = 'single-source'; 0 = 'unverified'</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>Drives the multi-source filter on the elevated feed</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>x_confidence_tier</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>cwz-roadevent-feed.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="23" t="inlineStr">
+        <is>
+          <t>5. Composition (CWZ 1.0)</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Sticky accumulation</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Evidence accumulates rather than flickering between refreshes</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Verification flags persist once earned (camera removal excepted), so a zone does not oscillate as individual sources come and go</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>x_connection_status</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>validation-ledger.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="24" t="inlineStr">
+        <is>
+          <t>5. Composition (CWZ 1.0)</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>WZDx output</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>The result is a spec-valid feed others can consume</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>Emitted as WZDx v4.2 / CWZ 1.0 WorkZoneRoadEvent features with is_start_position_verified and the x_* evidence fields</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>full feature</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>cwz-roadevent-feed.js, cwz-device-feed.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>6. Monitoring</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Feed health</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>The upstream source itself is alive</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Is DMS_View returning data? how many devices are stale? fetch success history per feed</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Surfaced in the validation panel and availability dimension</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>device-validation.js, feed-tracking-service.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="20" t="inlineStr">
+        <is>
+          <t>6. Monitoring</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>How much of the network actually has independent evidence</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>Share of active work zones with a connected device / any verification source</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>Reported, not enforced</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>device-validation.js, coverage-gap-analyzer.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="19" t="inlineStr">
+        <is>
+          <t>6. Monitoring</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Lifecycle</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Events are retired when they should be</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Event lifecycle manager ages out and closes events; camera tc_removed feeds the same decision</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>Event leaves the active set</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>event-lifecycle-manager.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="20" t="inlineStr">
+        <is>
+          <t>6. Monitoring</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>Exceptions / stewardship</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>A human is told when something needs attention</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>Work-zone exceptions raised to stewards (WZ_STEWARDS) via WZ_NOTIFY_WEBHOOK</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>Notification</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>wz-exceptions.js</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2289,7 +4430,7 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>37 registered state feeds - see 'State Feed Registry'</t>
+          <t>37 registered feeds covering 33 US states, plus DTCD, Quebec City and Austin TX - see 'State Feed Registry' and 'State Coverage Matrix'</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -2638,7 +4779,7 @@
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>Weather hazards on the corridor map; the single biggest gap-filler for the ~17 states with no public WZDx/511 feed; IPAWS context</t>
+          <t>Weather hazards on the corridor map; the ONLY source reaching the 16 states + DC with no event, camera or device feed; IPAWS context</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
@@ -25840,22 +27981,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="78" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="76" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>State key</t>
+          <t>Feed key</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
@@ -25865,25 +28007,30 @@
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
+          <t>State code</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
           <t>Feed type</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Format</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Enabled</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>Feed URL (key redacted)</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>Key required</t>
         </is>
@@ -25892,72 +28039,82 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>ca</t>
+          <t>az</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Arizona (Maricopa)</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
           <t>WZDx</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>json</t>
-        </is>
-      </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
+          <t>geojson</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>https://api.511.org/traffic/wzdx?api_key=</t>
-        </is>
-      </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>https://wzdxapi.aztech.org/construction</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>ca</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>Colorado DOT</t>
+          <t>California DOT</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>CWZ</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>WZDx</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
+          <t>geojson</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>https://data.cotrip.org/api/v1/cwz?apiKey=</t>
-        </is>
-      </c>
       <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>https://api.511.org/traffic/wzdx?api_key=</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -25966,183 +28123,208 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>co-wzdx</t>
+          <t>au</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Colorado DOT (WZDx Traditional)</t>
+          <t>City of Austin, TX</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
           <t>WZDx</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>json</t>
-        </is>
-      </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>geojson</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>https://data.cotrip.org/api/v1/wzdx?apiKey=</t>
-        </is>
-      </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>https://data.austintexas.gov/download/d9mm-cjw9</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>co</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Delaware DOT</t>
+          <t>Colorado DOT</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
           <t>WZDx</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>geojson</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>https://wzdx.e-dot.com/del_dot_feed_wzdx_v4.1.geojson</t>
-        </is>
-      </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>https://data.cotrip.org/api/v1/wzdx?apiKey=</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>fl</t>
+          <t>de</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Florida DOT</t>
+          <t>Delaware</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
           <t>WZDx</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>json</t>
-        </is>
-      </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>geojson</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>https://us-datacloud.one.network/fdot/feed.json?app_key=</t>
-        </is>
-      </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>https://wzdx.e-dot.com/del_dot_feed_wzdx_v4.1.geojson</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>hi</t>
+          <t>fl</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Hawaii DOT</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
           <t>WZDx</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>geojson</t>
-        </is>
-      </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
+          <t>json</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>https://ai.blyncsy.io/wzdx/hidot/feed</t>
-        </is>
-      </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>https://us-datacloud.one.network/fdot/feed.json?app_key=&lt;REDACTED&gt;</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>ga</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Idaho DOT</t>
+          <t>Georgia DOT</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
           <t>WZDx</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>geojson</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>https://511.idaho.gov/api/wzdx</t>
-        </is>
-      </c>
       <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>https://511ga.org/feeds/wzdx</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -26151,35 +28333,40 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>illinois</t>
+          <t>hi</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Hawaii</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Custom JSON</t>
+          <t>HI</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>WZDx</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
+          <t>geojson</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>https://travelmidwest.com/lmiga/incidents.json?path=GATEWAY.IL</t>
-        </is>
-      </c>
       <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>https://ai.blyncsy.io/wzdx/hidot/feed</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -26188,72 +28375,82 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>il</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Idaho</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
           <t>WZDx</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>json</t>
-        </is>
-      </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
+          <t>geojson</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>https://tims2go.tollway.state.il.us/wzdx/v4.2?api_key=</t>
-        </is>
-      </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>https://511.idaho.gov/api/wzdx</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>il</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Indiana</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>WZDx</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
+          <t>TMDD/CARS</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
           <t>json</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>https://in.carsprogram.org/carsapi_v1/api/wzdx</t>
-        </is>
-      </c>
       <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>https://travelmidwest.com/lmiga/incidents.json?path=GATEWAY.IL</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -26262,35 +28459,40 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>ia</t>
+          <t>in</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Indiana</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>WZDx</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>TMDD/CARS</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>xml</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>https://iowa-atms.cloud-q-free.com/api/rest/dataprism/wzdx/wzdxfeed</t>
-        </is>
-      </c>
       <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>https://inhub.carsprogram.org/data/feu-g.xml</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -26299,35 +28501,40 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>ia</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>WZDx</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>TMDD/CARS</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
+          <t>xml</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>https://ks.carsprogram.org/carsapi_v1/api/wzdx</t>
-        </is>
-      </c>
       <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>https://ia.carsprogram.org/hub/data/feu-g.xml</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -26336,35 +28543,40 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>ky</t>
+          <t>io</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Kentucky Transportation Cabinet</t>
+          <t>Iowa WZDx</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
           <t>WZDx</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>geojson</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>https://storage.googleapis.com/kytc-its-2020-openrecords/public/feeds/WZDx/kytc_wzdx_v4.1.geojson</t>
-        </is>
-      </c>
       <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>https://iowa-atms.cloud-q-free.com/api/rest/dataprism/wzdx/wzdxfeed</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -26373,35 +28585,40 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>la</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Louisiana DOTD</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>WZDx</t>
+          <t>KS</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>geojson</t>
+          <t>TMDD/CARS</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
+          <t>xml</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>https://wzdx.e-dot.com/la_dot_d_feed_wzdx_v4.1.geojson</t>
-        </is>
-      </c>
       <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>https://kscars.kandrive.gov/hub/data/feu-g.xml</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -26410,35 +28627,40 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>az</t>
+          <t>ky</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Maricopa County DOT</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
           <t>WZDx</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>geojson</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>https://wzdxapi.aztech.org/construction</t>
-        </is>
-      </c>
       <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>https://storage.googleapis.com/kytc-its-2020-openrecords/public/feeds/WZDx/kytc_wzdx_v4.1.geojson</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -26447,35 +28669,40 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>la</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Maryland DOT</t>
+          <t>Louisiana</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
           <t>WZDx</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>geojson</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>https://filter.ritis.org/wzdx_v4.1/mdot.geojson</t>
-        </is>
-      </c>
       <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>https://wzdx.e-dot.com/la_dot_d_feed_wzdx_v4.1.geojson</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -26484,35 +28711,40 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>ma</t>
+          <t>md</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Massachusetts DOT</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
           <t>WZDx</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>geojson</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>https://feed.massdot-swzm.com/massdot_wzdx_v4.1_work_zone_feed.geojson</t>
-        </is>
-      </c>
       <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>https://filter.ritis.org/wzdx_v4.1/mdot.geojson</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -26521,35 +28753,40 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>mi</t>
+          <t>ma</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Michigan DOT</t>
+          <t>Massachusetts</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
           <t>WZDx</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>json</t>
-        </is>
-      </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
+          <t>geojson</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>https://mdotridedata.state.mi.us/api/v1/organization/michigan_department_of_transportation/dataset/work_zone_information/query</t>
-        </is>
-      </c>
       <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>https://feed.massdot-swzm.com/massdot_wzdx_v4.1_work_zone_feed.geojson</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -26568,25 +28805,30 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>WZDx</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>TMDD/CARS</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
+          <t>xml</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>https://mn.carsprogram.org/carsapi_v1/api/wzdx</t>
-        </is>
-      </c>
       <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>https://mn.carsprogram.org/hub/data/feu-g.xml</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -26595,35 +28837,40 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>mo</t>
+          <t>mi</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Missouri DOT</t>
+          <t>Mississippi</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
           <t>WZDx</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>geojson</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>https://scc.ridsi-dash.com:5000/wzdx.geojson</t>
-        </is>
-      </c>
       <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>https://api.mdottraffic.com/prod/v3/data/wzdx</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -26632,35 +28879,40 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>nebraska</t>
+          <t>mo</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>FEU-G</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>xml</t>
+          <t>WZDx</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
+          <t>json</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>https://ne.carsprogram.org/hub/data/feu-g.xml</t>
-        </is>
-      </c>
       <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>https://traveler.modot.org/timconfig/feed/desktop/mo_wzdx.json</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -26679,25 +28931,30 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>CARS</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
+          <t>TMDD/CARS</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
           <t>xml</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>https://ne.carsprogram.org/hub/data/feu-g.xml</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -26706,7 +28963,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>nevada</t>
+          <t>nv</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -26716,25 +28973,30 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Custom JSON</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
+          <t>TMDD/CARS</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
           <t>json</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>https://www.nvroads.com/api/v2/get/roadconditions</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -26743,35 +29005,40 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>nv</t>
+          <t>nj</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Nevada</t>
+          <t>New Jersey</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Nevada DOT</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>WZDx</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
+          <t>geojson</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>https://www.nvroads.com/api/v2/get/roadconditions</t>
-        </is>
-      </c>
       <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>https://smartworkzones.njit.edu/nj/wzdx</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -26780,35 +29047,40 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>newjersey</t>
+          <t>nm</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>New Jersey</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>RSS</t>
+          <t>NM</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>xml</t>
+          <t>WZDx</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
+          <t>geojson</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>https://511nj.org/client/rest/rss/RSSAllNJActiveEvents</t>
-        </is>
-      </c>
       <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>https://ai.blyncsy.io/wzdx/nmdot/feed</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -26817,35 +29089,40 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>nj</t>
+          <t>ny</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>New Jersey</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
           <t>WZDx</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>json</t>
-        </is>
-      </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
+          <t>geojson</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>https://smartworkzones.njit.edu/nj/wzdx</t>
-        </is>
-      </c>
       <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>https://511ny.org/api/wzdx</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -26854,72 +29131,82 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>nm</t>
+          <t>nc</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>New Mexico DOT</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
           <t>WZDx</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>geojson</t>
-        </is>
-      </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
+          <t>json</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>https://ai.blyncsy.io/wzdx/nmdot/feed</t>
-        </is>
-      </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>https://us-datacloud.one.network/wzdx-north-carolina.json?app_key=&lt;REDACTED&gt;</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>ny</t>
+          <t>oh</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>New York DOT</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>WZDx</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>geojson</t>
+          <t>TMDD/CARS</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
+          <t>json</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>https://511ny.org/api/wzdx</t>
-        </is>
-      </c>
       <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>https://publicapi.ohgo.com/api/v1/constructions</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -26928,35 +29215,40 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>nc</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>North Carolina DOT</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
           <t>WZDx</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>geojson</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>https://us-datacloud.one.network/wzdx-north-carolina.json?app_key=&lt;REDACTED&gt;</t>
-        </is>
-      </c>
       <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>https://oktraffic.org/api/Geojsons/workzones?&amp;access_token=&lt;REDACTED&gt;</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -26965,35 +29257,40 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>oh</t>
+          <t>pa</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Pennsylvania DOT</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
           <t>WZDx</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>json</t>
-        </is>
-      </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
+          <t>geojson</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>https://publicapi.ohgo.com/api/work-zones/wzdx/4.2?api-key=</t>
-        </is>
-      </c>
       <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>https://atms.paturnpike.com/api/WZDxWorkZoneFeed?api_key=</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -27002,74 +29299,84 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>dt</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>PurposeBuilt DTCD (CWZ 1.0)</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
           <t>WZDx</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>geojson</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>https://oktraffic.org/api/Geojsons/workzones?&amp;access_token=</t>
-        </is>
-      </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>https://feeds.purposebuilt.systems/cwz</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>pa</t>
+          <t>qu</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Quebec City</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
           <t>WZDx</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>json</t>
-        </is>
-      </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
+          <t>geojson</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>https://atms.paturnpike.com/api/WZDxWorkZoneFeed?api_key=</t>
-        </is>
-      </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>https://quebec.gewi.com/wzdx/pull</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -27081,32 +29388,37 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Texas (Austin)</t>
+          <t>Texas DOT</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
           <t>WZDx</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>geojson</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>https://api.drivetexas.org/api/conditions.wzdx.geojson?key=</t>
-        </is>
-      </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>https://api.drivetexas.org/api/conditions.wzdx.geojson</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -27123,25 +29435,30 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>WZDx</t>
+          <t>UT</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
+          <t>TMDD/CARS</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
           <t>json</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="F35" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
+      <c r="G35" s="8" t="inlineStr">
         <is>
           <t>https://udottraffic.utah.gov/wzdx/udot/v40/data</t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr">
+      <c r="H35" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -27160,25 +29477,30 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
           <t>WZDx</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>json</t>
-        </is>
-      </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
+          <t>geojson</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>https://data.511-atis-ttrip-prod.iteriscloud.com/smarterRoads/workzone/workZoneJSON/current/workZone.json?token=</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -27192,30 +29514,35 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Washington State DOT</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
           <t>WZDx</t>
         </is>
       </c>
-      <c r="D37" s="8" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>geojson</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="F37" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
+      <c r="G37" s="8" t="inlineStr">
         <is>
           <t>https://wzdx.wsdot.wa.gov/api/v4/WorkZoneFeed</t>
         </is>
       </c>
-      <c r="G37" s="8" t="inlineStr">
+      <c r="H37" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -27229,42 +29556,2422 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Wisconsin DOT</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
+          <t>WI</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
           <t>WZDx</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>json</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>https://511wi.gov/api/wzdx</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G38"/>
+  <autoFilter ref="A1:H38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="66" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Work-zone event feed</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Feed key(s) / type</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Cameras</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Camera count</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>DMS / devices</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Device count</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>NWS weather</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Channels</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Gap note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>Alabama</t>
+        </is>
+      </c>
+      <c r="C2" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr"/>
+      <c r="E2" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr"/>
+      <c r="G2" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H2" s="28" t="inlineStr"/>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="28" t="inlineStr">
+        <is>
+          <t>ALGO Traffic - no public API</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="27" t="inlineStr">
+        <is>
+          <t>AK</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>Alaska</t>
+        </is>
+      </c>
+      <c r="C3" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr"/>
+      <c r="E3" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr"/>
+      <c r="G3" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H3" s="28" t="inlineStr"/>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="28" t="inlineStr">
+        <is>
+          <t>511AK custom JSON - documented in STATE_COVERAGE.md but NOT in the production registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>az (WZDx)</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>644</v>
+      </c>
+      <c r="G4" s="16" t="inlineStr">
+        <is>
+          <t>Key needed</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Arkansas</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr"/>
+      <c r="E5" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr"/>
+      <c r="G5" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H5" s="28" t="inlineStr"/>
+      <c r="I5" s="28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J5" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="28" t="inlineStr">
+        <is>
+          <t>No public feed found</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>ca (WZDx)</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>3340</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>1016</v>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>Colorado</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D7" s="31" t="inlineStr">
+        <is>
+          <t>co (WZDx)</t>
+        </is>
+      </c>
+      <c r="E7" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F7" s="31" t="inlineStr"/>
+      <c r="G7" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" s="31" t="inlineStr"/>
+      <c r="I7" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J7" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="31" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>Connecticut</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="inlineStr"/>
+      <c r="E8" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr"/>
+      <c r="G8" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" s="28" t="inlineStr"/>
+      <c r="I8" s="28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="28" t="inlineStr">
+        <is>
+          <t>No public feed found</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>Delaware</t>
+        </is>
+      </c>
+      <c r="C9" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D9" s="31" t="inlineStr">
+        <is>
+          <t>de (WZDx)</t>
+        </is>
+      </c>
+      <c r="E9" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F9" s="31" t="inlineStr"/>
+      <c r="G9" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" s="31" t="inlineStr"/>
+      <c r="I9" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J9" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="31" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>District of Columbia</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="inlineStr"/>
+      <c r="E10" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="inlineStr"/>
+      <c r="G10" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10" s="28" t="inlineStr"/>
+      <c r="I10" s="28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J10" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="28" t="inlineStr">
+        <is>
+          <t>No public feed found</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>fl (WZDx)</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>1669</v>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>1047</v>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" s="8" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>ga (WZDx)</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>4043</v>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="30" t="inlineStr">
+        <is>
+          <t>HI</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="inlineStr">
+        <is>
+          <t>hi (WZDx)</t>
+        </is>
+      </c>
+      <c r="E13" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F13" s="31" t="inlineStr"/>
+      <c r="G13" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" s="31" t="inlineStr"/>
+      <c r="I13" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J13" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="31" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Idaho</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>id (WZDx)</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>457</v>
+      </c>
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t>Key needed</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B15" s="31" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="inlineStr">
+        <is>
+          <t>il (TMDD/CARS)</t>
+        </is>
+      </c>
+      <c r="E15" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F15" s="31" t="inlineStr"/>
+      <c r="G15" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" s="31" t="inlineStr"/>
+      <c r="I15" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J15" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="31" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="30" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="inlineStr">
+        <is>
+          <t>Indiana</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D16" s="31" t="inlineStr">
+        <is>
+          <t>in (TMDD/CARS)</t>
+        </is>
+      </c>
+      <c r="E16" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F16" s="31" t="inlineStr"/>
+      <c r="G16" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H16" s="31" t="inlineStr"/>
+      <c r="I16" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J16" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="31" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>ia (TMDD/CARS); io (WZDx)</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>1252</v>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>via DMS_View</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>Iowa's DMS comes through the DMS_View ArcGIS layer (dms-corroboration.js / device-ingest.js), not the multi-state device-adapters registry - so it is not in the 9 counted there</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="30" t="inlineStr">
+        <is>
+          <t>KS</t>
+        </is>
+      </c>
+      <c r="B18" s="31" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D18" s="31" t="inlineStr">
+        <is>
+          <t>ks (TMDD/CARS)</t>
+        </is>
+      </c>
+      <c r="E18" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F18" s="31" t="inlineStr"/>
+      <c r="G18" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H18" s="31" t="inlineStr"/>
+      <c r="I18" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J18" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="31" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Kentucky</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>ky (WZDx)</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr"/>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" s="8" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Louisiana</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>la (WZDx)</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>336</v>
+      </c>
+      <c r="G20" s="16" t="inlineStr">
+        <is>
+          <t>Key needed</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>405</v>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>101</v>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>No event feed, but cameras AND a portable-DMS feed are live - an event feed is the only missing piece</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Maryland</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>md (WZDx)</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>295</v>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="30" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B23" s="31" t="inlineStr">
+        <is>
+          <t>Massachusetts</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D23" s="31" t="inlineStr">
+        <is>
+          <t>ma (WZDx)</t>
+        </is>
+      </c>
+      <c r="E23" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F23" s="31" t="inlineStr"/>
+      <c r="G23" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H23" s="31" t="inlineStr"/>
+      <c r="I23" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J23" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" s="31" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="27" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="B24" s="28" t="inlineStr">
+        <is>
+          <t>Michigan</t>
+        </is>
+      </c>
+      <c r="C24" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D24" s="28" t="inlineStr"/>
+      <c r="E24" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F24" s="28" t="inlineStr"/>
+      <c r="G24" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H24" s="28" t="inlineStr"/>
+      <c r="I24" s="28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J24" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="28" t="inlineStr">
+        <is>
+          <t>Mi Drive - no public WZDx. NOTE: the local dev states.db mislabels the 'mi' key as Michigan; production correctly has it as Mississippi</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>MN</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Minnesota</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>mn (TMDD/CARS)</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>1528</v>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr"/>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" s="8" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="B26" s="31" t="inlineStr">
+        <is>
+          <t>Mississippi</t>
+        </is>
+      </c>
+      <c r="C26" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D26" s="31" t="inlineStr">
+        <is>
+          <t>mi (WZDx)</t>
+        </is>
+      </c>
+      <c r="E26" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F26" s="31" t="inlineStr"/>
+      <c r="G26" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H26" s="31" t="inlineStr"/>
+      <c r="I26" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J26" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" s="31" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="B27" s="31" t="inlineStr">
+        <is>
+          <t>Missouri</t>
+        </is>
+      </c>
+      <c r="C27" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D27" s="31" t="inlineStr">
+        <is>
+          <t>mo (WZDx)</t>
+        </is>
+      </c>
+      <c r="E27" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F27" s="31" t="inlineStr"/>
+      <c r="G27" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H27" s="31" t="inlineStr"/>
+      <c r="I27" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J27" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" s="31" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B28" s="28" t="inlineStr">
+        <is>
+          <t>Montana</t>
+        </is>
+      </c>
+      <c r="C28" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D28" s="28" t="inlineStr"/>
+      <c r="E28" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F28" s="28" t="inlineStr"/>
+      <c r="G28" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H28" s="28" t="inlineStr"/>
+      <c r="I28" s="28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J28" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="28" t="inlineStr">
+        <is>
+          <t>No public feed found</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="30" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="B29" s="31" t="inlineStr">
+        <is>
+          <t>Nebraska</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D29" s="31" t="inlineStr">
+        <is>
+          <t>ne (TMDD/CARS)</t>
+        </is>
+      </c>
+      <c r="E29" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F29" s="31" t="inlineStr"/>
+      <c r="G29" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H29" s="31" t="inlineStr"/>
+      <c r="I29" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J29" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" s="31" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Nevada</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>nv (TMDD/CARS)</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>640</v>
+      </c>
+      <c r="G30" s="16" t="inlineStr">
+        <is>
+          <t>Key needed</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="B31" s="28" t="inlineStr">
+        <is>
+          <t>New Hampshire</t>
+        </is>
+      </c>
+      <c r="C31" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D31" s="28" t="inlineStr"/>
+      <c r="E31" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F31" s="28" t="inlineStr"/>
+      <c r="G31" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H31" s="28" t="inlineStr"/>
+      <c r="I31" s="28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J31" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="28" t="inlineStr">
+        <is>
+          <t>No public feed found</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="30" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="B32" s="31" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D32" s="31" t="inlineStr">
+        <is>
+          <t>nj (WZDx)</t>
+        </is>
+      </c>
+      <c r="E32" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F32" s="31" t="inlineStr"/>
+      <c r="G32" s="34" t="inlineStr">
+        <is>
+          <t>Key needed</t>
+        </is>
+      </c>
+      <c r="H32" s="31" t="inlineStr"/>
+      <c r="I32" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J32" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" s="31" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="30" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="B33" s="31" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D33" s="31" t="inlineStr">
+        <is>
+          <t>nm (WZDx)</t>
+        </is>
+      </c>
+      <c r="E33" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F33" s="31" t="inlineStr"/>
+      <c r="G33" s="34" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="H33" s="31" t="inlineStr"/>
+      <c r="I33" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J33" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" s="31" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>ny (WZDx)</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>1871</v>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>919</v>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>nc (WZDx)</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>1140</v>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>Key needed</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr"/>
+      <c r="I35" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J35" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K35" s="8" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="27" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="B36" s="28" t="inlineStr">
+        <is>
+          <t>North Dakota</t>
+        </is>
+      </c>
+      <c r="C36" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D36" s="28" t="inlineStr"/>
+      <c r="E36" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F36" s="28" t="inlineStr"/>
+      <c r="G36" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H36" s="28" t="inlineStr"/>
+      <c r="I36" s="28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J36" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="28" t="inlineStr">
+        <is>
+          <t>No public feed found</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="30" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B37" s="31" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="C37" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D37" s="31" t="inlineStr">
+        <is>
+          <t>oh (TMDD/CARS)</t>
+        </is>
+      </c>
+      <c r="E37" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F37" s="31" t="inlineStr"/>
+      <c r="G37" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H37" s="31" t="inlineStr"/>
+      <c r="I37" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J37" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" s="31" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Oklahoma</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>ok (WZDx)</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr"/>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>167</v>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="27" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B39" s="28" t="inlineStr">
+        <is>
+          <t>Oregon</t>
+        </is>
+      </c>
+      <c r="C39" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D39" s="28" t="inlineStr"/>
+      <c r="E39" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F39" s="28" t="inlineStr"/>
+      <c r="G39" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H39" s="28" t="inlineStr"/>
+      <c r="I39" s="28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J39" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="28" t="inlineStr">
+        <is>
+          <t>TripCheck - API key required, not yet registered</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>pa (WZDx)</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>1536</v>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>962</v>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="27" t="inlineStr">
+        <is>
+          <t>RI</t>
+        </is>
+      </c>
+      <c r="B41" s="28" t="inlineStr">
+        <is>
+          <t>Rhode Island</t>
+        </is>
+      </c>
+      <c r="C41" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D41" s="28" t="inlineStr"/>
+      <c r="E41" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F41" s="28" t="inlineStr"/>
+      <c r="G41" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H41" s="28" t="inlineStr"/>
+      <c r="I41" s="28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J41" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="28" t="inlineStr">
+        <is>
+          <t>No public feed found</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="27" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="B42" s="28" t="inlineStr">
+        <is>
+          <t>South Carolina</t>
+        </is>
+      </c>
+      <c r="C42" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D42" s="28" t="inlineStr"/>
+      <c r="E42" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F42" s="28" t="inlineStr"/>
+      <c r="G42" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H42" s="28" t="inlineStr"/>
+      <c r="I42" s="28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J42" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="28" t="inlineStr">
+        <is>
+          <t>No public feed found</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="27" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B43" s="28" t="inlineStr">
+        <is>
+          <t>South Dakota</t>
+        </is>
+      </c>
+      <c r="C43" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D43" s="28" t="inlineStr"/>
+      <c r="E43" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F43" s="28" t="inlineStr"/>
+      <c r="G43" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H43" s="28" t="inlineStr"/>
+      <c r="I43" s="28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J43" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="28" t="inlineStr">
+        <is>
+          <t>No public feed found</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="27" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B44" s="28" t="inlineStr">
+        <is>
+          <t>Tennessee</t>
+        </is>
+      </c>
+      <c r="C44" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D44" s="28" t="inlineStr"/>
+      <c r="E44" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F44" s="28" t="inlineStr"/>
+      <c r="G44" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H44" s="28" t="inlineStr"/>
+      <c r="I44" s="28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J44" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="28" t="inlineStr">
+        <is>
+          <t>511 service exists, no documented REST API</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="17" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Texas</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>au (WZDx); tx (WZDx)</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>1005</v>
+      </c>
+      <c r="G45" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="inlineStr"/>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J45" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K45" s="8" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="18" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Utah</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>ut (TMDD/CARS)</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>2075</v>
+      </c>
+      <c r="G46" s="16" t="inlineStr">
+        <is>
+          <t>Key needed</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr"/>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="27" t="inlineStr">
+        <is>
+          <t>VT</t>
+        </is>
+      </c>
+      <c r="B47" s="28" t="inlineStr">
+        <is>
+          <t>Vermont</t>
+        </is>
+      </c>
+      <c r="C47" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D47" s="28" t="inlineStr"/>
+      <c r="E47" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F47" s="28" t="inlineStr"/>
+      <c r="G47" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H47" s="28" t="inlineStr"/>
+      <c r="I47" s="28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J47" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="28" t="inlineStr">
+        <is>
+          <t>No public feed found</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="30" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B48" s="31" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="C48" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D48" s="31" t="inlineStr">
+        <is>
+          <t>va (WZDx)</t>
+        </is>
+      </c>
+      <c r="E48" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F48" s="31" t="inlineStr"/>
+      <c r="G48" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H48" s="31" t="inlineStr"/>
+      <c r="I48" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J48" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" s="31" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="17" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>wa (WZDx)</t>
+        </is>
+      </c>
+      <c r="E49" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr"/>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I49" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J49" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K49" s="8" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="27" t="inlineStr">
+        <is>
+          <t>WV</t>
+        </is>
+      </c>
+      <c r="B50" s="28" t="inlineStr">
+        <is>
+          <t>West Virginia</t>
+        </is>
+      </c>
+      <c r="C50" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D50" s="28" t="inlineStr"/>
+      <c r="E50" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F50" s="28" t="inlineStr"/>
+      <c r="G50" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H50" s="28" t="inlineStr"/>
+      <c r="I50" s="28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J50" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="28" t="inlineStr">
+        <is>
+          <t>No public feed found</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="30" t="inlineStr">
+        <is>
+          <t>WI</t>
+        </is>
+      </c>
+      <c r="B51" s="31" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="C51" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D51" s="31" t="inlineStr">
+        <is>
+          <t>wi (WZDx)</t>
+        </is>
+      </c>
+      <c r="E51" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F51" s="31" t="inlineStr"/>
+      <c r="G51" s="34" t="inlineStr">
+        <is>
+          <t>Key needed</t>
+        </is>
+      </c>
+      <c r="H51" s="31" t="inlineStr"/>
+      <c r="I51" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J51" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" s="31" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="27" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="B52" s="28" t="inlineStr">
+        <is>
+          <t>Wyoming</t>
+        </is>
+      </c>
+      <c r="C52" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D52" s="28" t="inlineStr"/>
+      <c r="E52" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F52" s="28" t="inlineStr"/>
+      <c r="G52" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H52" s="28" t="inlineStr"/>
+      <c r="I52" s="28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J52" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="28" t="inlineStr">
+        <is>
+          <t>No public feed found</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="17" t="inlineStr"/>
+      <c r="B53" s="17" t="inlineStr">
+        <is>
+          <t>TOTALS of 51 (50 states + DC)</t>
+        </is>
+      </c>
+      <c r="C53" s="17" t="inlineStr">
+        <is>
+          <t>33 states</t>
+        </is>
+      </c>
+      <c r="D53" s="17" t="inlineStr"/>
+      <c r="E53" s="17" t="inlineStr">
+        <is>
+          <t>15 states</t>
+        </is>
+      </c>
+      <c r="F53" s="17" t="n">
+        <v>21941</v>
+      </c>
+      <c r="G53" s="17" t="inlineStr">
+        <is>
+          <t>9 live + IA</t>
+        </is>
+      </c>
+      <c r="H53" s="17" t="n">
+        <v>4601</v>
+      </c>
+      <c r="I53" s="17" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J53" s="17" t="inlineStr"/>
+      <c r="K53" s="17" t="inlineStr">
+        <is>
+          <t>17 have weather only: AL, AK, AR, CT, DC, MI, MT, NH, ND, OR, RI, SC, SD, TN, VT, WV, WY</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K52"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -28990,7 +33697,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -29301,7 +34008,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -29956,7 +34663,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -30869,2063 +35576,4 @@
   <autoFilter ref="A1:J20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G55"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="74" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Stage</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>What it validates</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Rule / threshold as coded</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>On fail</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Output field</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Implemented in</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="19" t="inlineStr">
-        <is>
-          <t>0. Ingest / normalize</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Route normalization</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>Free-text route strings from 37 different feeds resolve to one canonical route id</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>Regex ladder: I-nnn first (ramp strings embed it), then US-nnn, then &lt;ST&gt;-nnn. 'I 380', 'I-380', 'RAMP: I 80E TO 100TH ST' all -&gt; 'I-380'/'I-80'</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>Returns null -&gt; the record cannot be route-matched and is skipped by the matcher</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>route / rawRoute</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>device-workzone-matcher.js normalizeRoute</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="20" t="inlineStr">
-        <is>
-          <t>0. Ingest / normalize</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>Direction normalization</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>Carriageway direction is one of N/S/E/W/BOTH</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>First letter after uppercasing; 'Both'/'B' -&gt; BOTH; anything else -&gt; null (neutral, not a reject)</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>null = unknown, treated as neutral rather than a mismatch</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>direction</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>device-workzone-matcher.js normalizeDir</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>0. Ingest / normalize</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Coordinate sanity</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Lat/lon are real and not a null-island artifact</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Both finite, not (0,0), |lat| &lt;= 90, |lon| &lt;= 180</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Record dropped at normalize()</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>coordinates</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>device-adapters.js normalize</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>1. Geometry</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Missing content</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Event has geometry and some human content</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>No geometry -&gt; drop. Empty description AND empty location -&gt; drop</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Event filtered out entirely</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>geometry-validator.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>1. Geometry</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Fallback-geometry rejection</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Geometry is not an interpolated straight line masquerading as road shape</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>geometrySource in ('straight_line','straight') -&gt; drop</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Event filtered out</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>geometry-validator.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>1. Geometry</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>2-point LineString collapse</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>A 2-point line carries no road shape, so it must not render as a road</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>LineString with exactly 2 coordinates -&gt; converted to a Point at the midpoint</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>Downgraded to a marker, not dropped</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>_geometryFixed</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>geometry-validator.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>1. Geometry</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Curvature test (long lines)</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>A very long 'closure' line actually follows the road rather than cutting across it</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>chord &gt; 50 mi AND path length / chord &lt; 1.05 (under 5% curvature) -&gt; drop</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Event filtered out</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>geometry-validator.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>1. Geometry</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Type validity</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Point/LineString/Polygon/Multi* are structurally well formed</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Point needs 2 coords; LineString &gt;= 2; Polygon outer ring &gt;= 4; Multi* non-empty; unknown type -&gt; drop</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>Event filtered out</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>geometry-validator.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>2. Feed quality (DQI)</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Completeness (20%)</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Required WZDx fields are actually populated across the feed</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Share of events carrying end time, description, geometry, severity, lanes affected</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Lowers the feed's DQI and letter grade</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>dqi.completeness</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>feed-quality-scorer.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>2. Feed quality (DQI)</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Freshness (15%)</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>The feed is being updated and events are not stale</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Update latency + stale-event share</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>Lowers DQI</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>dqi.freshness</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>feed-quality-scorer.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>2. Feed quality (DQI)</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Accuracy (20%)</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Geometry validates and the payload matches schema</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Geometry validation pass rate + schema compliance</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Lowers DQI</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>dqi.accuracy</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>feed-quality-scorer.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>2. Feed quality (DQI)</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Availability (15%)</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>The endpoint answers reliably</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Fetch success / failure history per feed key</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>Lowers DQI; feeds an outage signal</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>dqi.availability</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>feed-quality-scorer.js + feed-tracking-service.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>2. Feed quality (DQI)</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Standardization (15%)</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>WZDx compliance, valid event types, ITIS codes</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Share of events using spec-valid enumerations</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Lowers DQI</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>dqi.standardization</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>feed-quality-scorer.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>2. Feed quality (DQI)</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Timeliness (10%)</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>No future-dated or long-expired events</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Event age distribution + future-dating check</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>Lowers DQI</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>dqi.timeliness</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>feed-quality-scorer.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>2. Feed quality (DQI)</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Usability (5%)</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Contact info, restrictions, work-zone type present</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Share of events with actionable detail</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Lowers DQI</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>dqi.usability</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>feed-quality-scorer.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>2. Feed quality (DQI)</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Composite + grade</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>One comparable number per state feed</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Weighted mean of the 7 dimensions (weights sum to 1.0) -&gt; letter grade A-F</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>Published on the state report cards</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>dqi.overall / grade</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>feed-quality-scorer.js, report-card-service.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>3. Event confidence</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Completeness (35%)</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Per-EVENT (not per-feed) trustworthiness: are the critical fields there</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>id, eventType, start time, finite non-zero lat/lng, and the rest of the critical field set</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Lowers the event's 0-100 score</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>confidence.score</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>event-confidence.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>3. Event confidence</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Geospatial precision (15%)</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Point coordinates AND real linestring geometry present</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Both lat/lng and a LineString score full credit</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>Lowers score</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>confidence.score</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>event-confidence.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>3. Event confidence</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Temporal validity (20%)</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Has a start, has an end, is not stale</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>startTime present, end time present, age within bounds</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Lowers score</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>confidence.score</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>event-confidence.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>3. Event confidence</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Description quality (15%)</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>The narrative is specific, not boilerplate</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Length / specificity heuristic on the description</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>Lowers score</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>confidence.score</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>event-confidence.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>3. Event confidence</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Verification (15%)</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>DOT operator comments corroborate the record</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Presence of corroborating operator narrative</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Lowers score</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>confidence.score</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>event-confidence.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>3. Event confidence</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Level banding</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Score becomes an operator-facing label</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>VERIFIED &gt;= 85, HIGH 70-84, MEDIUM 50-69, LOW 30-49, UNVERIFIED &lt; 30</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>Drives downstream filtering and display</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>confidence.level</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>event-confidence.js levelFromScore</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="21" t="inlineStr">
-        <is>
-          <t>4. Validator - DEVICE</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Gate 1: route</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>The arrow board / portable DMS is on the same route as the zone</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>Device route must equal the zone's normalized route. A route-LESS device is allowed through on the other gates but starts at 30 base credit instead of 40</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Return null - not a match</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>x_cwz_connected</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>device-workzone-matcher.js scoreMatch</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="22" t="inlineStr">
-        <is>
-          <t>4. Validator - DEVICE</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Gate 2: carriageway</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>The device is not on the opposite side of a divided highway</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Same direction = +25; either side BOTH = +12; opposite = reject; unknown on either side = neutral (0, no reject)</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>Opposite carriageway -&gt; reject</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>x_cwz_connected</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>device-workzone-matcher.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="21" t="inlineStr">
-        <is>
-          <t>4. Validator - DEVICE</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Gate 3: proximity</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>The device is close enough to plausibly belong to the zone</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Distance to the zone geometry (snapped onto the line, or to the point) must be &lt;= 1600 m (~1 mi). Spatial credit = 25 * (1 - d/1600). &lt;= 150 m counts as effectively on the zone</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>Beyond 1600 m -&gt; reject</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>x_connected_devices[].distanceM</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>device-workzone-matcher.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="22" t="inlineStr">
-        <is>
-          <t>4. Validator - DEVICE</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>Gate 4: upstream (Field Escort rule)</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>The board sits UPSTREAM of the zone in the served travel direction - traffic has not already passed it</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>isUpstream() against the matched reference point. Skipped when the device is alongside the zone or direction is unknown/BOTH</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>Downstream -&gt; reject (it belongs to a different zone)</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>reasons[]</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>device-workzone-matcher.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="21" t="inlineStr">
-        <is>
-          <t>4. Validator - DEVICE</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>Temporal</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>The device reported recently and inside the zone's active window</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>Fresh = reported within 2 h (+5). Also checks the report timestamp falls between event start and end</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>Stale still matches but scores 5 lower</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>fresh</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>device-workzone-matcher.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="22" t="inlineStr">
-        <is>
-          <t>4. Validator - DEVICE</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Deployment state</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>The board is actually ON, not blank / in transit</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>mode.displaying true (arrow/chevron/caution pattern) = +5</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>An off board can match but never AUTO-links (requireOnForAuto)</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>mode.displaying</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>device-workzone-matcher.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="21" t="inlineStr">
-        <is>
-          <t>4. Validator - DEVICE</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>Scoring + banding</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Confidence is an honest number; questionable links go to a human</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>confidence = (40 if route known else 30) + dir + spatial + temporal + deploy. &gt;= 75 auto-link; 60-74 review queue; &lt; 60 no link. 'off' or &gt; 800 m block AUTO without lowering the score</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>Below 60 no link; 60-74 surfaced for confirmation</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>x_connected_confidence</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>device-workzone-matcher.js DEFAULTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="22" t="inlineStr">
-        <is>
-          <t>4. Validator - DEVICE</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>Independent post-check</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>The auto-links are audited using signals the matcher did NOT use</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>Self-location parsed out of the device NAME ('SS2426 - I-35 NB @ MM 71.6') vs the feed's Route/Direction fields; message-vs-zone-type clash (the rest-area case); temporal; far / 'dir both' downgrades</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>Link downgraded and surfaced in the validation panel</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>validation flags</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>device-validation.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="21" t="inlineStr">
-        <is>
-          <t>4. Validator - CAMERA</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>Match (free, no network)</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>There is a camera that could plausibly see the zone</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>Nearest camera on the SAME interstate within 1500 m</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>No camera -&gt; no camera check is attempted</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>x_camera_id</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>camera-validation.js matchCamera</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="22" t="inlineStr">
-        <is>
-          <t>4. Validator - CAMERA</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Active-now gate</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>Do not spend a vision call on a zone WZDx says is not running</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>isActiveNow(): now between start and end. null (no start date) also skips</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>Skipped, no cost</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>camera-validation.js isActiveNow</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="21" t="inlineStr">
-        <is>
-          <t>4. Validator - CAMERA</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>Vision inference</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Temporary traffic control is physically deployed, not stored</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>ONE inference on the still snapshot returning {work_zone, deployed, staged_only, devices[arrow-board,cones,barrels,drums,signs,workers,tma], confidence}. Only DEPLOYED counts - staged/stored cones do not</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>No detection = soft negative (proximity is not line-of-sight; most feeds have no PTZ/heading)</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>x_camera_verified, x_camera_detected</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>camera-validation.js detect</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="22" t="inlineStr">
-        <is>
-          <t>4. Validator - CAMERA</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>Cost controls</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>Vision spend cannot run away</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>Gated on a vision key being set (otherwise available:false, $0); per-snapshot-URL cache TTL 10 min; on-demand only, never in a timer or the shared refresh; cheapest model, tiny token budget; max 25 zones per scan</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>Silently unavailable rather than billing</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>camera-validation.js, camera-scan.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="21" t="inlineStr">
-        <is>
-          <t>4. Validator - CAMERA</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>Check-count policy</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>A closure is never re-billed indefinitely</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>Check #1 only within 90 min of start. If it sees nothing, ONE follow-up after 30 min. Hard cap 2 vision checks per closure ever. A non-detection while vision is off does NOT consume a check</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>Ledger enforces the cap across restarts</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>camera_check_ledger.checks</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>camera-scan.js, camera-check-ledger.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="22" t="inlineStr">
-        <is>
-          <t>4. Validator - CAMERA</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>Removal detection (daily)</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>A multi-day zone that is actually finished stops being elevated even if WZDx still lists it</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>Confirmed multi-day closures get one check per 24 h; traffic control gone -&gt; tc_removed. This is the ONLY validator that can take verification away</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>Zone drops out of the verified set</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>tc_removed</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="inlineStr">
-        <is>
-          <t>camera-check-ledger.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="21" t="inlineStr">
-        <is>
-          <t>4. Validator - PROBE (TomTom)</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>Category filter</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>Only genuine work-zone incidents count as corroboration</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>iconCategory in {7 lane closed, 8 road closed, 9 road works}; lat/lon finite</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>Other incident types ignored</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>tomtom-corroboration.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="22" t="inlineStr">
-        <is>
-          <t>4. Validator - PROBE (TomTom)</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>Spatial + route match</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>The independent incident is at the same place on the same road</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>Same interstate, within 1500 m (maxM default)</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t>No stamp applied</t>
-        </is>
-      </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>x_tomtom_corroborated</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t>tomtom-corroboration.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="21" t="inlineStr">
-        <is>
-          <t>4. Validator - PROBE (TomTom)</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>Independence + cost</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>This is a genuinely non-DOT opinion, obtained cheaply</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>TomTom's own probe network, not the state that published the zone. Reuses the already-cached incident set - zero extra API calls in the corroborator. Upstream fetch is budget- and rate-capped with a circuit breaker</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>Absence never demotes a zone</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>x_tomtom_corroborated</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>tomtom-corroboration.js, tomtom-incidents.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="22" t="inlineStr">
-        <is>
-          <t>4. Validator - DMS</t>
-        </is>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>Message content (strong)</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>The sign genuinely states roadwork or a closure</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>WZ_STRONG regex: ROAD WORK, WORK ZONE, LANE CLOSED, &lt;n&gt; LANES CLOSED, SHOULDER CLOSED/WORK, ROAD CLOSED, CLOSED AT/AHEAD/&lt;day&gt;, RAMP CLOSED, DETOUR, CONSTRUCTION, PAVING, MILLING, BRIDGE WORK, WORK AHEAD</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>No match -&gt; not evidence</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>x_dms_corroborated</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>dms-corroboration.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="21" t="inlineStr">
-        <is>
-          <t>4. Validator - DMS</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>Message content (exclusions)</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>The unrelated messages a board cycles through are never counted</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>WZ_EXCLUDE regex rejects Amber/Silver/Blue alerts, seat-belt / drive-sober / phone-down / move-over campaigns, travel times and '&lt;n&gt; MIN', weather (wind, fog, snow, ice), crashes and disabled vehicles, game-day traffic, election notices</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>Rejected even if a STRONG token also appears</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>dms-corroboration.js isWorkZoneMsg</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="22" t="inlineStr">
-        <is>
-          <t>4. Validator - DMS</t>
-        </is>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>Weak-token removal</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="inlineStr">
-        <is>
-          <t>Bare tokens that also appear in incident and generic messages do not qualify</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>Deliberately dropped from the old rule: a lone CLOSED, MERGE, WORKERS, REDUCED SPEED, EXPECT DELAY</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>Requires a specific phrase instead</t>
-        </is>
-      </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t>dms-corroboration.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="21" t="inlineStr">
-        <is>
-          <t>4. Validator - DMS</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>Spatial + route match</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>The sign is near the zone, on the same road when known</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>Same interstate when known, within a few miles; zone must be active now</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>No stamp applied</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>x_dms_corroborated</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>dms-corroboration.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="22" t="inlineStr">
-        <is>
-          <t>4. Validator - DMS</t>
-        </is>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>Independence</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
-        <is>
-          <t>A human operator in a different system posted this</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>DMS text is authored by an operator, not exported by the same automated WZDx pipeline being validated</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t>Absence never demotes</t>
-        </is>
-      </c>
-      <c r="F45" s="8" t="inlineStr">
-        <is>
-          <t>x_dms_corroborated</t>
-        </is>
-      </c>
-      <c r="G45" s="8" t="inlineStr">
-        <is>
-          <t>dms-corroboration.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="23" t="inlineStr">
-        <is>
-          <t>5. Composition (CWZ 1.0)</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>Positive-only semantics</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>A validator can only ever RAISE confidence</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>All four validators are positive-only. The single exception is the camera validator's daily removal check, which can withdraw verification</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>Missing evidence is never treated as disproof</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>x_verification[]</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>cwz-roadevent-feed.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="24" t="inlineStr">
-        <is>
-          <t>5. Composition (CWZ 1.0)</t>
-        </is>
-      </c>
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t>Source set</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="inlineStr">
-        <is>
-          <t>Which independent systems agree about this zone</t>
-        </is>
-      </c>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>x_verification collects any of: device, camera, tomtom, dms</t>
-        </is>
-      </c>
-      <c r="E47" s="8" t="inlineStr">
-        <is>
-          <t>Empty array = unverified</t>
-        </is>
-      </c>
-      <c r="F47" s="8" t="inlineStr">
-        <is>
-          <t>x_verification</t>
-        </is>
-      </c>
-      <c r="G47" s="8" t="inlineStr">
-        <is>
-          <t>cwz-roadevent-feed.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="23" t="inlineStr">
-        <is>
-          <t>5. Composition (CWZ 1.0)</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>Corroboration count</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>How many INDEPENDENT sources agree - kept separate from how many devices are present</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>x_verification_count = number of distinct validators. x_connected_device_count is the physical device count and can be 0 while the zone is still corroborated by camera/TomTom/DMS</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>The two numbers are never conflated</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>x_verification_count</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>cwz-roadevent-feed.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="24" t="inlineStr">
-        <is>
-          <t>5. Composition (CWZ 1.0)</t>
-        </is>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>Confidence tier</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t>Operator-facing banding of the corroboration count</t>
-        </is>
-      </c>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>&gt;= 2 sources = 'multi-source'; exactly 1 = 'single-source'; 0 = 'unverified'</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t>Drives the multi-source filter on the elevated feed</t>
-        </is>
-      </c>
-      <c r="F49" s="8" t="inlineStr">
-        <is>
-          <t>x_confidence_tier</t>
-        </is>
-      </c>
-      <c r="G49" s="8" t="inlineStr">
-        <is>
-          <t>cwz-roadevent-feed.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="23" t="inlineStr">
-        <is>
-          <t>5. Composition (CWZ 1.0)</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>Sticky accumulation</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>Evidence accumulates rather than flickering between refreshes</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>Verification flags persist once earned (camera removal excepted), so a zone does not oscillate as individual sources come and go</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>x_connection_status</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>validation-ledger.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="24" t="inlineStr">
-        <is>
-          <t>5. Composition (CWZ 1.0)</t>
-        </is>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
-        <is>
-          <t>WZDx output</t>
-        </is>
-      </c>
-      <c r="C51" s="8" t="inlineStr">
-        <is>
-          <t>The result is a spec-valid feed others can consume</t>
-        </is>
-      </c>
-      <c r="D51" s="8" t="inlineStr">
-        <is>
-          <t>Emitted as WZDx v4.2 / CWZ 1.0 WorkZoneRoadEvent features with is_start_position_verified and the x_* evidence fields</t>
-        </is>
-      </c>
-      <c r="E51" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F51" s="8" t="inlineStr">
-        <is>
-          <t>full feature</t>
-        </is>
-      </c>
-      <c r="G51" s="8" t="inlineStr">
-        <is>
-          <t>cwz-roadevent-feed.js, cwz-device-feed.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="19" t="inlineStr">
-        <is>
-          <t>6. Monitoring</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>Feed health</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>The upstream source itself is alive</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>Is DMS_View returning data? how many devices are stale? fetch success history per feed</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>Surfaced in the validation panel and availability dimension</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>device-validation.js, feed-tracking-service.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="20" t="inlineStr">
-        <is>
-          <t>6. Monitoring</t>
-        </is>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>Coverage</t>
-        </is>
-      </c>
-      <c r="C53" s="8" t="inlineStr">
-        <is>
-          <t>How much of the network actually has independent evidence</t>
-        </is>
-      </c>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>Share of active work zones with a connected device / any verification source</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="inlineStr">
-        <is>
-          <t>Reported, not enforced</t>
-        </is>
-      </c>
-      <c r="F53" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G53" s="8" t="inlineStr">
-        <is>
-          <t>device-validation.js, coverage-gap-analyzer.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="19" t="inlineStr">
-        <is>
-          <t>6. Monitoring</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>Lifecycle</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>Events are retired when they should be</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>Event lifecycle manager ages out and closes events; camera tc_removed feeds the same decision</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>Event leaves the active set</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>event-lifecycle-manager.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="20" t="inlineStr">
-        <is>
-          <t>6. Monitoring</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>Exceptions / stewardship</t>
-        </is>
-      </c>
-      <c r="C55" s="8" t="inlineStr">
-        <is>
-          <t>A human is told when something needs attention</t>
-        </is>
-      </c>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>Work-zone exceptions raised to stewards (WZ_STEWARDS) via WZ_NOTIFY_WEBHOOK</t>
-        </is>
-      </c>
-      <c r="E55" s="8" t="inlineStr">
-        <is>
-          <t>Notification</t>
-        </is>
-      </c>
-      <c r="F55" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G55" s="8" t="inlineStr">
-        <is>
-          <t>wz-exceptions.js</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G55"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/Corridor_Communicator_API_Inventory.xlsx
+++ b/docs/Corridor_Communicator_API_Inventory.xlsx
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'External APIs Consumed'!$A$1:$G$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Published Feeds'!$A$1:$F$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Camera Sources'!$A$1:$H$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'DMS + Device Sources'!$A$1:$J$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'DMS + Device Sources'!$A$1:$K$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Validation Logic'!$A$1:$G$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -36,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -98,8 +98,9 @@
       <b val="1"/>
       <color rgb="000F6B78"/>
     </font>
+    <font/>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -124,6 +125,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF6E5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F4EA"/>
       </patternFill>
     </fill>
   </fills>
@@ -153,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -249,6 +255,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -616,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C133"/>
+  <dimension ref="A1:C139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2283,6 +2295,41 @@
       <c r="A133" t="inlineStr">
         <is>
           <t>8 more device feeds unlock with a free 511 key: UT LA AZ NC NJ WI NV ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Connected arrow boards</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>66 arrow boards total, from only 2 states: Iowa 62 (DMS_View) and Washington 4 (WZDx v4 Device Feed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Every other device feed returns portable DMS, not arrow boards - 425 portable units across NY/PA/ME/OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Washington is the ONLY source with a properly typed device_type field; Iowa's are inferred from a device-name regex</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Vendor arrow-board fleets (iCone, Ver-Mac, HaulHub, Drivewyze) are not ingested directly - that is the MITRE partnership path</t>
         </is>
       </c>
     </row>
@@ -34669,22 +34716,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>State</t>
@@ -34717,863 +34765,916 @@
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
+          <t>ARROW BOARDS</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Portable DMS</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
           <t>Actively displaying</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Portable units</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>Key required</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>IA</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>Iowa (DMS corroboration validator)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Iowa DOT (DMS_View)</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>ArcGIS FeatureServer</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>https://services.arcgis.com/8lRhdTsQyJpO52F1/ArcGIS/rest/services/DMS_View/FeatureServer/0/query</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>not counted in this pull</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="inlineStr"/>
-      <c r="G2" s="8" t="inlineStr"/>
-      <c r="H2" s="8" t="inlineStr"/>
-      <c r="I2" s="8" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="G2" s="35" t="n">
+        <v>62</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J2" s="8" t="inlineStr">
-        <is>
-          <t>Primary DMS source for the DMS validator + device ingest; 10-min cache</t>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>The primary connected-device source. Arrow boards are Solar Tech - AB and iCone - AB units reporting real patterns (Right/Left Chevron sequential, Caution Four Corner flashing). NOTE: type is inferred from a NAME regex (/-\s*AB\b|arrow/i), not a typed field - a vendor naming a board differently is silently classed as DMS. Ingested via dms-corroboration.js / device-ingest.js, not device-adapters.js</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Arizona</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>CARS/OneStop 511</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>https://az511.com/api/v2/get/messagesigns</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>SKIPPED - no key</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr"/>
-      <c r="G3" s="5" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr"/>
+      <c r="H3" s="8" t="inlineStr"/>
+      <c r="I3" s="8" t="inlineStr"/>
+      <c r="J3" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="K3" s="8" t="inlineStr">
         <is>
           <t>Free key required</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>California</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Caltrans CWWP2 CMS (12 districts)</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>https://cwwp2.dot.ca.gov/data/d&lt;N&gt;/cms/cmsStatusD&lt;NN&gt;.json</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="5" t="n">
         <v>1016</v>
       </c>
-      <c r="G4" s="8" t="n">
+      <c r="G4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="8" t="n">
+      <c r="H4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="I4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J4" s="8" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>Some districts intermittently 500 and are skipped</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>FL</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Florida</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>ArcGIS FeatureServer</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>https://gis.fdot.gov/arcgis/rest/services/DIVAS_MessageBoard/FeatureServer/0/query</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="8" t="n">
         <v>1047</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="8" t="n">
         <v>520</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>Fixed DMS with live message text</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Idaho</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>CARS/OneStop 511</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>https://511.idaho.gov/api/v2/get/messagesigns</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>SKIPPED - no key</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Free key required</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Kentucky</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>ArcGIS FeatureServer</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>https://services2.arcgis.com/CcI36Pduqd0OR4W9/.../dmsSigns_2020/FeatureServer/0/query</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="G7" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="H7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>83</v>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>Fixed DMS with live message text</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Idaho</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Louisiana</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>CARS/OneStop 511</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>https://511.idaho.gov/api/v2/get/messagesigns</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>https://511la.org/api/v2/get/messagesigns</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>SKIPPED - no key</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="8" t="inlineStr"/>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="J6" s="8" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>Free key required</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Kentucky</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>ArcGIS FeatureServer</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>https://services2.arcgis.com/CcI36Pduqd0OR4W9/.../dmsSigns_2020/FeatureServer/0/query</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>ArcGIS MapServer</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>https://arcgisserver.maine.gov/arcgis/rest/services/mdot/MaineDOT_Dynamic/MapServer/111/query</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="F7" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>83</v>
-      </c>
-      <c r="H7" s="5" t="n">
+      <c r="F9" s="8" t="n">
+        <v>101</v>
+      </c>
+      <c r="G9" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="H9" s="8" t="n">
+        <v>101</v>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>Fixed DMS with live message text</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>LA</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Louisiana</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>Portable = trailer installation type</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Maryland</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>ArcGIS MapServer (CHART)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>https://chartimap1.sha.maryland.gov/arcgis/rest/services/CHART/DMS/MapServer/0/query</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>295</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>212</v>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>Route/direction parsed from location string</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Nevada</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>CARS/OneStop 511</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>https://511la.org/api/v2/get/messagesigns</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>https://www.nvroads.com/api/v2/get/messagesigns</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>SKIPPED - no key</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr"/>
-      <c r="G8" s="8" t="inlineStr"/>
-      <c r="H8" s="8" t="inlineStr"/>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr"/>
+      <c r="G11" s="8" t="inlineStr"/>
+      <c r="H11" s="8" t="inlineStr"/>
+      <c r="I11" s="8" t="inlineStr"/>
+      <c r="J11" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="J8" s="8" t="inlineStr">
+      <c r="K11" s="8" t="inlineStr">
         <is>
           <t>Free key required</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>ME</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Maine</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>CARS/OneStop 511</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>https://511nj.org/api/getmessagesigns</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>SKIPPED - no key</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>Free key required</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Custom REST (NMRoads)</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>https://servicev4.nmroads.com/RealMapWAR/GetMessageSigns</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>ERROR: certificate has expired</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr"/>
+      <c r="G13" s="8" t="inlineStr"/>
+      <c r="H13" s="8" t="inlineStr"/>
+      <c r="I13" s="8" t="inlineStr"/>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>TLS certificate expired as of the pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>CARS/OneStop 511 (keyless path)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>https://511ny.org/api/getmessagesigns?format=json</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>919</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>919</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>Keyless; 175 portable units detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>CARS/OneStop 511</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>https://www.drivenc.gov/api/v2/get/messagesigns</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>SKIPPED - no key</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr"/>
+      <c r="G15" s="8" t="inlineStr"/>
+      <c r="H15" s="8" t="inlineStr"/>
+      <c r="I15" s="8" t="inlineStr"/>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>Free key required</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Oklahoma</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Custom REST (oktraffic.org)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>https://oktraffic.org/api/Devices + /api/DmsStatuses</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>167</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>NTCIP MULTI tags stripped from message text</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>ArcGIS MapServer</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>https://arcgisserver.maine.gov/arcgis/rest/services/mdot/MaineDOT_Dynamic/MapServer/111/query</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>https://gis.penndot.gov/arcgis/rest/services/tsams/tsams/MapServer/17/query</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="F9" s="5" t="n">
-        <v>101</v>
-      </c>
-      <c r="G9" s="5" t="n">
+      <c r="F17" s="8" t="n">
+        <v>962</v>
+      </c>
+      <c r="G17" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="5" t="n">
-        <v>101</v>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="H17" s="8" t="n">
+        <v>109</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>Portable = trailer installation type</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Maryland</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>ArcGIS MapServer (CHART)</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>https://chartimap1.sha.maryland.gov/arcgis/rest/services/CHART/DMS/MapServer/0/query</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>Portable = trailer / Type A-B structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Utah</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>CARS/OneStop 511</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>https://www.udottraffic.utah.gov/api/v2/get/messagesigns</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>SKIPPED - no key</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>Free key required</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>WZDx v4 Device Feed</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>https://wzdx.wsdot.wa.gov/api/v4/DeviceFeed</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="F10" s="8" t="n">
-        <v>295</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>212</v>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="F19" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t>Route/direction parsed from location string</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>NV</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Nevada</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="K19" s="8" t="inlineStr">
+        <is>
+          <t>Only true WZDx device feed in the set - real arrow boards</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>WI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>CARS/OneStop 511</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>https://www.nvroads.com/api/v2/get/messagesigns</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>https://511wi.gov/api/v2/get/messagesigns</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
         <is>
           <t>SKIPPED - no key</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>Free key required</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>NJ</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>New Jersey</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>CARS/OneStop 511</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>https://511nj.org/api/getmessagesigns</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>SKIPPED - no key</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr"/>
-      <c r="G12" s="8" t="inlineStr"/>
-      <c r="H12" s="8" t="inlineStr"/>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="inlineStr">
-        <is>
-          <t>Free key required</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>NM</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>New Mexico</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Custom REST (NMRoads)</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>https://servicev4.nmroads.com/RealMapWAR/GetMessageSigns</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>ERROR: certificate has expired</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr"/>
-      <c r="G13" s="5" t="inlineStr"/>
-      <c r="H13" s="5" t="inlineStr"/>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>TLS certificate expired as of the pull</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>CARS/OneStop 511 (keyless path)</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>https://511ny.org/api/getmessagesigns?format=json</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>919</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>919</v>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>175</v>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="inlineStr">
-        <is>
-          <t>Keyless; 175 portable units detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>North Carolina</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>CARS/OneStop 511</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>https://www.drivenc.gov/api/v2/get/messagesigns</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>SKIPPED - no key</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr"/>
-      <c r="G15" s="5" t="inlineStr"/>
-      <c r="H15" s="5" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>Free key required</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Oklahoma</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Custom REST (oktraffic.org)</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>https://oktraffic.org/api/Devices + /api/DmsStatuses</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>167</v>
-      </c>
-      <c r="G16" s="8" t="n">
-        <v>51</v>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J16" s="8" t="inlineStr">
-        <is>
-          <t>NTCIP MULTI tags stripped from message text</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Pennsylvania</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>ArcGIS MapServer</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>https://gis.penndot.gov/arcgis/rest/services/tsams/tsams/MapServer/17/query</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>962</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>109</v>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>Portable = trailer / Type A-B structure</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>UT</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Utah</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>CARS/OneStop 511</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>https://www.udottraffic.utah.gov/api/v2/get/messagesigns</t>
-        </is>
-      </c>
-      <c r="E18" s="14" t="inlineStr">
-        <is>
-          <t>SKIPPED - no key</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr"/>
-      <c r="G18" s="8" t="inlineStr"/>
-      <c r="H18" s="8" t="inlineStr"/>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J18" s="8" t="inlineStr">
-        <is>
-          <t>Free key required</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>WA</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Washington</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>WZDx v4 Device Feed</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>https://wzdx.wsdot.wa.gov/api/v4/DeviceFeed</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>Only true WZDx device feed in the set - real arrow boards</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>WI</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Wisconsin</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>CARS/OneStop 511</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>https://511wi.gov/api/v2/get/messagesigns</t>
-        </is>
-      </c>
-      <c r="E20" s="14" t="inlineStr">
-        <is>
-          <t>SKIPPED - no key</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr"/>
-      <c r="G20" s="8" t="inlineStr"/>
-      <c r="H20" s="8" t="inlineStr"/>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J20" s="8" t="inlineStr">
-        <is>
-          <t>Free key required</t>
-        </is>
-      </c>
-    </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr"/>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>TOTAL (feeds that returned)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr"/>
-      <c r="D21" s="18" t="inlineStr"/>
-      <c r="E21" s="18" t="inlineStr"/>
-      <c r="F21" s="18" t="n">
-        <v>4601</v>
-      </c>
-      <c r="G21" s="18" t="n">
-        <v>1789</v>
-      </c>
-      <c r="H21" s="18" t="n">
-        <v>429</v>
-      </c>
-      <c r="I21" s="18" t="inlineStr"/>
-      <c r="J21" s="18" t="inlineStr"/>
+      <c r="A21" s="17" t="inlineStr"/>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>TOTAL (feeds returning data)</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr"/>
+      <c r="D21" s="17" t="inlineStr"/>
+      <c r="E21" s="17" t="inlineStr"/>
+      <c r="F21" s="17" t="n">
+        <v>4720</v>
+      </c>
+      <c r="G21" s="36" t="n">
+        <v>66</v>
+      </c>
+      <c r="H21" s="17" t="n">
+        <v>486</v>
+      </c>
+      <c r="I21" s="17" t="inlineStr"/>
+      <c r="J21" s="17" t="inlineStr"/>
+      <c r="K21" s="17" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J20"/>
+  <autoFilter ref="A1:K21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/Corridor_Communicator_API_Inventory.xlsx
+++ b/docs/Corridor_Communicator_API_Inventory.xlsx
@@ -629,7 +629,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C139"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -657,6 +657,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
@@ -718,6 +719,7 @@
         <v>8</v>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
@@ -775,6 +777,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
@@ -2179,6 +2182,7 @@
         </is>
       </c>
     </row>
+    <row r="113"/>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
@@ -2214,6 +2218,7 @@
         </is>
       </c>
     </row>
+    <row r="119"/>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
@@ -2242,6 +2247,7 @@
         </is>
       </c>
     </row>
+    <row r="124"/>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
@@ -2256,6 +2262,7 @@
         </is>
       </c>
     </row>
+    <row r="127"/>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
@@ -2298,6 +2305,7 @@
         </is>
       </c>
     </row>
+    <row r="134"/>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
@@ -2308,14 +2316,14 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>66 arrow boards total, from only 2 states: Iowa 62 (DMS_View) and Washington 4 (WZDx v4 Device Feed)</t>
+          <t>73 arrow boards total, from 3 states: Iowa 62 (DMS_View), Oklahoma 7 (Trailer class), Washington 4 (WZDx v4 Device Feed)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Every other device feed returns portable DMS, not arrow boards - 425 portable units across NY/PA/ME/OK</t>
+          <t>Every other device feed returns portable or fixed DMS, not arrow boards - 486 portable DMS units across NY/PA/ME/OK</t>
         </is>
       </c>
     </row>
@@ -2345,7 +2353,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G55"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -4404,7 +4412,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -6169,7 +6177,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I512"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
@@ -28029,7 +28037,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -29650,7 +29658,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K53"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -32025,7 +32033,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G46"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -33751,7 +33759,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -34062,7 +34070,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -34717,7 +34725,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
@@ -35450,11 +35458,11 @@
       <c r="F16" s="5" t="n">
         <v>167</v>
       </c>
-      <c r="G16" s="5" t="n">
-        <v>0</v>
+      <c r="G16" s="35" t="n">
+        <v>7</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>51</v>
@@ -35466,7 +35474,7 @@
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>NTCIP MULTI tags stripped from message text</t>
+          <t>ODOT's /api/DeviceTypeNames models "Trailer" as deviceTypeNameId 9 under its own deviceTypeId 4 - a non-DMS field-device class, and none appear in /DmsStatuses (no sign text). 10 exist; 3 report 0,0 and are dropped. They carry no route, so the matcher infers it from the matched zone at reduced base credit. Fixed 2026-09-03 - previously typed 'dms' and not flagged portable, so all 10 were invisible.</t>
         </is>
       </c>
     </row>
@@ -35664,10 +35672,10 @@
         <v>4720</v>
       </c>
       <c r="G21" s="36" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="H21" s="17" t="n">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="I21" s="17" t="inlineStr"/>
       <c r="J21" s="17" t="inlineStr"/>

--- a/docs/Corridor_Communicator_API_Inventory.xlsx
+++ b/docs/Corridor_Communicator_API_Inventory.xlsx
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'External APIs Consumed'!$A$1:$G$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Published Feeds'!$A$1:$F$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Camera Sources'!$A$1:$H$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'DMS + Device Sources'!$A$1:$K$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'DMS + Device Sources'!$A$1:$L$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Validation Logic'!$A$1:$G$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -629,7 +629,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C139"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -2316,14 +2316,14 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>73 arrow boards total, from 3 states: Iowa 62 (DMS_View), Oklahoma 7 (Trailer class), Washington 4 (WZDx v4 Device Feed)</t>
+          <t>74 arrow boards total, from 3 states: Iowa 62 (DMS_View), Oklahoma 7 (Trailer class), Washington 5 (WZDx v4 Device Feed)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Every other device feed returns portable or fixed DMS, not arrow boards - 486 portable DMS units across NY/PA/ME/OK</t>
+          <t>853 of the remaining devices (PennDOT 752, MaineDOT 101) are static ASSET INVENTORY with no telemetry - excluded from adjudication, kept for coverage</t>
         </is>
       </c>
     </row>
@@ -2352,8 +2352,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:G57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -4396,6 +4396,80 @@
       <c r="G55" s="8" t="inlineStr">
         <is>
           <t>wz-exceptions.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="22" t="inlineStr">
+        <is>
+          <t>4. Validator - DEVICE</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>Asset-inventory exclusion</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>A record from a static GIS asset layer is never treated as device telemetry, in either direction</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>Adapters whose source is an inventory layer (PennDOT TSAMS, MaineDOT - no message field, no timestamp) set inventory:true. matchDevices drops those to unmatched before the auto/review split</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>Excluded from links AND from review; kept in the roster for coverage reporting</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>device.inventory</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t>device-adapters.js, device-workzone-matcher.js matchDevices</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="22" t="inlineStr">
+        <is>
+          <t>4. Validator - DEVICE</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Non-existent device exclusion</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>Only hardware actually in the field is ingested</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>PennDOT TSAMS carries DEVICE_STATUS 'Planned' (185), 'Programmed' (83) and 'Down' (20) alongside 752 'Existing/Standby'; the adapter where-clause now keeps only Existing/Standby. Kentucky likewise filters dmsStatus='Online'</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>Filtered at ingest - never reaches the matcher</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>device-adapters.js</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4486,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -6177,7 +6251,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I512"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
@@ -28037,7 +28111,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -29658,7 +29732,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K53"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -32033,7 +32107,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G46"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -33759,7 +33833,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -34070,7 +34144,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -34724,23 +34798,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:L21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="54" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="74" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>State</t>
@@ -34768,7 +34843,7 @@
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>Signs / devices</t>
+          <t>Devices</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
@@ -34783,15 +34858,20 @@
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
-          <t>Actively displaying</t>
+          <t>Live / displaying</t>
         </is>
       </c>
       <c r="J1" s="4" t="inlineStr">
         <is>
+          <t>Inventory only (no telemetry)</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
           <t>Key required</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -34834,17 +34914,20 @@
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J2" s="5" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>The primary connected-device source. Arrow boards are Solar Tech - AB and iCone - AB units reporting real patterns (Right/Left Chevron sequential, Caution Four Corner flashing). NOTE: type is inferred from a NAME regex (/-\s*AB\b|arrow/i), not a typed field - a vendor naming a board differently is silently classed as DMS. Ingested via dms-corroboration.js / device-ingest.js, not device-adapters.js</t>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>The primary connected-device source. Arrow boards are Solar Tech - AB / iCone - AB units reporting real patterns. Type is inferred from a NAME regex, not a typed field - a board named differently is silently classed as DMS. Ingested via dms-corroboration.js / device-ingest.js, not device-adapters.js</t>
         </is>
       </c>
     </row>
@@ -34878,14 +34961,15 @@
       <c r="G3" s="8" t="inlineStr"/>
       <c r="H3" s="8" t="inlineStr"/>
       <c r="I3" s="8" t="inlineStr"/>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
-        <is>
-          <t>Free key required</t>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>Free 511 key not set - no key (set AZ_511_KEY)</t>
         </is>
       </c>
     </row>
@@ -34927,14 +35011,17 @@
       <c r="I4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>Some districts intermittently 500 and are skipped</t>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>Caltrans CWWP2 CMS across 12 districts; some districts intermittently 500 and are skipped.</t>
         </is>
       </c>
     </row>
@@ -34965,7 +35052,7 @@
         </is>
       </c>
       <c r="F5" s="8" t="n">
-        <v>1047</v>
+        <v>1138</v>
       </c>
       <c r="G5" s="8" t="n">
         <v>0</v>
@@ -34974,16 +35061,19 @@
         <v>0</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>520</v>
-      </c>
-      <c r="J5" s="8" t="inlineStr">
+        <v>569</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K5" s="8" t="inlineStr">
-        <is>
-          <t>Fixed DMS with live message text</t>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>Live message text, no device-type field in the layer (DIVAS_MessageBoard). No arrow boards to miss.</t>
         </is>
       </c>
     </row>
@@ -35017,14 +35107,15 @@
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>Free key required</t>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>Free 511 key not set - no key (set ID_511_KEY)</t>
         </is>
       </c>
     </row>
@@ -35055,7 +35146,7 @@
         </is>
       </c>
       <c r="F7" s="8" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G7" s="8" t="n">
         <v>0</v>
@@ -35064,16 +35155,19 @@
         <v>0</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>83</v>
-      </c>
-      <c r="J7" s="8" t="inlineStr">
+        <v>82</v>
+      </c>
+      <c r="J7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
-        <is>
-          <t>Fixed DMS with live message text</t>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>Live telemetry (message + timestamp). FIXED 2026-09-03: 2 'Offline' signs were being ingested; now filtered to dmsStatus='Online' (90 -&gt; 88).</t>
         </is>
       </c>
     </row>
@@ -35107,14 +35201,15 @@
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>Free key required</t>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Free 511 key not set - no key (set LA_511_KEY)</t>
         </is>
       </c>
     </row>
@@ -35156,14 +35251,17 @@
       <c r="I9" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="8" t="inlineStr">
+      <c r="J9" s="34" t="n">
+        <v>101</v>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
-        <is>
-          <t>Portable = trailer installation type</t>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>ASSET INVENTORY, not telemetry: all 101 are Ver-Mac 'Trailer Mounted' / 'Changable Message Sign' assets with no message and no timestamp. Flagged inventory 2026-09-03 so they cannot be adjudicated.</t>
         </is>
       </c>
     </row>
@@ -35205,14 +35303,17 @@
       <c r="I10" s="5" t="n">
         <v>212</v>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>Route/direction parsed from location string</t>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Live message text (CHART). No device-type field in the layer. No arrow boards to miss.</t>
         </is>
       </c>
     </row>
@@ -35246,14 +35347,15 @@
       <c r="G11" s="8" t="inlineStr"/>
       <c r="H11" s="8" t="inlineStr"/>
       <c r="I11" s="8" t="inlineStr"/>
-      <c r="J11" s="8" t="inlineStr">
+      <c r="J11" s="8" t="inlineStr"/>
+      <c r="K11" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr">
-        <is>
-          <t>Free key required</t>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>Free 511 key not set - no key (set NV_511_KEY)</t>
         </is>
       </c>
     </row>
@@ -35287,14 +35389,15 @@
       <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>Free key required</t>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>Free 511 key not set - no key (set NJ_511_KEY)</t>
         </is>
       </c>
     </row>
@@ -35328,14 +35431,15 @@
       <c r="G13" s="8" t="inlineStr"/>
       <c r="H13" s="8" t="inlineStr"/>
       <c r="I13" s="8" t="inlineStr"/>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="J13" s="8" t="inlineStr"/>
+      <c r="K13" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K13" s="8" t="inlineStr">
-        <is>
-          <t>TLS certificate expired as of the pull</t>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>NMRoads TLS certificate has expired - feed unreachable.</t>
         </is>
       </c>
     </row>
@@ -35366,25 +35470,28 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>919</v>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
+        <v>925</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>Keyless; 175 portable units detected</t>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>Keyless CARS/OneStop path. 175 units name-matched as portable.</t>
         </is>
       </c>
     </row>
@@ -35418,14 +35525,15 @@
       <c r="G15" s="8" t="inlineStr"/>
       <c r="H15" s="8" t="inlineStr"/>
       <c r="I15" s="8" t="inlineStr"/>
-      <c r="J15" s="8" t="inlineStr">
+      <c r="J15" s="8" t="inlineStr"/>
+      <c r="K15" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr">
-        <is>
-          <t>Free key required</t>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>Free 511 key not set - no key (set NC_511_KEY)</t>
         </is>
       </c>
     </row>
@@ -35465,16 +35573,19 @@
         <v>47</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
+        <v>45</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>ODOT's /api/DeviceTypeNames models "Trailer" as deviceTypeNameId 9 under its own deviceTypeId 4 - a non-DMS field-device class, and none appear in /DmsStatuses (no sign text). 10 exist; 3 report 0,0 and are dropped. They carry no route, so the matcher infers it from the matched zone at reduced base credit. Fixed 2026-09-03 - previously typed 'dms' and not flagged portable, so all 10 were invisible.</t>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>ODOT models "Trailer" as deviceTypeNameId 9 under its own deviceTypeId 4 - a non-DMS class, absent from /DmsStatuses. 10 exist, 3 report 0,0 and drop. FIXED 2026-09-03: were typed 'dms' and not flagged portable, so all 10 were invisible.</t>
         </is>
       </c>
     </row>
@@ -35505,25 +35616,28 @@
         </is>
       </c>
       <c r="F17" s="8" t="n">
-        <v>962</v>
+        <v>752</v>
       </c>
       <c r="G17" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="I17" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="J17" s="34" t="n">
+        <v>752</v>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K17" s="8" t="inlineStr">
-        <is>
-          <t>Portable = trailer / Type A-B structure</t>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>ASSET INVENTORY, not telemetry: every record is ITS_DEVICE_TYPE 'DMS' with no message and no timestamp. FIXED 2026-09-03: the layer also carried 185 'Planned' + 83 'Programmed' + 20 'Down' devices that are not in the field - now filtered to Existing/Standby (1040 -&gt; 752).</t>
         </is>
       </c>
     </row>
@@ -35557,14 +35671,15 @@
       <c r="G18" s="5" t="inlineStr"/>
       <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>Free key required</t>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>Free 511 key not set - no key (set UT_511_KEY)</t>
         </is>
       </c>
     </row>
@@ -35595,25 +35710,28 @@
         </is>
       </c>
       <c r="F19" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G19" s="35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="J19" s="8" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="J19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr">
-        <is>
-          <t>Only true WZDx device feed in the set - real arrow boards</t>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t>The only feed with a properly typed WZDx device_type field - genuine arrow boards.</t>
         </is>
       </c>
     </row>
@@ -35647,14 +35765,15 @@
       <c r="G20" s="5" t="inlineStr"/>
       <c r="H20" s="5" t="inlineStr"/>
       <c r="I20" s="5" t="inlineStr"/>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>Free key required</t>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>Free 511 key not set - no key (set WI_511_KEY)</t>
         </is>
       </c>
     </row>
@@ -35669,20 +35788,23 @@
       <c r="D21" s="17" t="inlineStr"/>
       <c r="E21" s="17" t="inlineStr"/>
       <c r="F21" s="17" t="n">
-        <v>4720</v>
+        <v>4606</v>
       </c>
       <c r="G21" s="36" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H21" s="17" t="n">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="I21" s="17" t="inlineStr"/>
-      <c r="J21" s="17" t="inlineStr"/>
+      <c r="J21" s="30" t="n">
+        <v>853</v>
+      </c>
       <c r="K21" s="17" t="inlineStr"/>
+      <c r="L21" s="17" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K21"/>
+  <autoFilter ref="A1:L21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>